--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$233</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$237</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7538" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7661" uniqueCount="764">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2079,6 +2079,42 @@
   </si>
   <si>
     <t>Organization.telecom:mailbox-mss.extension:emailType</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.url</t>
+  </si>
+  <si>
+    <t>http://interopsante.org/fhir/StructureDefinition/FrContactPointEmailType</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.value[x]</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
+  &lt;code value="MSSANTE"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>http://interopsante.org/fhir/ValueSet/fr-email-type</t>
   </si>
   <si>
     <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
@@ -2678,7 +2714,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ233"/>
+  <dimension ref="A1:AJ237"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="80.17578125" customWidth="true" bestFit="true"/>
@@ -24119,7 +24155,7 @@
         <v>623</v>
       </c>
       <c r="D210" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E210" s="2"/>
       <c r="F210" t="s" s="2">
@@ -24146,9 +24182,7 @@
       <c r="M210" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="N210" t="s" s="2">
-        <v>105</v>
-      </c>
+      <c r="N210" s="2"/>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
         <v>73</v>
@@ -24217,11 +24251,9 @@
         <v>664</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C211" t="s" s="2">
         <v>665</v>
       </c>
+      <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
         <v>73</v>
       </c>
@@ -24233,7 +24265,7 @@
         <v>81</v>
       </c>
       <c r="H211" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I211" t="s" s="2">
         <v>73</v>
@@ -24242,13 +24274,13 @@
         <v>73</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>666</v>
+        <v>96</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>667</v>
+        <v>97</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>668</v>
+        <v>98</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
@@ -24299,27 +24331,27 @@
         <v>73</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI211" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>626</v>
+        <v>667</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -24327,10 +24359,10 @@
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H212" t="s" s="2">
         <v>73</v>
@@ -24339,20 +24371,18 @@
         <v>73</v>
       </c>
       <c r="J212" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>627</v>
+        <v>479</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N212" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N212" s="2"/>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>73</v>
@@ -24362,7 +24392,7 @@
         <v>73</v>
       </c>
       <c r="S212" t="s" s="2">
-        <v>670</v>
+        <v>73</v>
       </c>
       <c r="T212" t="s" s="2">
         <v>73</v>
@@ -24377,51 +24407,51 @@
         <v>73</v>
       </c>
       <c r="X212" t="s" s="2">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="Y212" t="s" s="2">
-        <v>629</v>
+        <v>73</v>
       </c>
       <c r="Z212" t="s" s="2">
-        <v>630</v>
+        <v>73</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB212" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC212" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD212" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE212" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>631</v>
+        <v>109</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI212" t="s" s="2">
-        <v>632</v>
+        <v>93</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>633</v>
+        <v>669</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -24435,35 +24465,33 @@
         <v>81</v>
       </c>
       <c r="H213" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I213" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>672</v>
+        <v>205</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>635</v>
+        <v>206</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O213" t="s" s="2">
-        <v>637</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q213" s="2"/>
       <c r="R213" t="s" s="2">
-        <v>73</v>
+        <v>670</v>
       </c>
       <c r="S213" t="s" s="2">
         <v>73</v>
@@ -24505,27 +24533,27 @@
         <v>73</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>638</v>
+        <v>209</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH213" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI213" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>639</v>
+        <v>672</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -24542,26 +24570,22 @@
         <v>73</v>
       </c>
       <c r="I214" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J214" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>640</v>
+        <v>213</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="N214" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="O214" t="s" s="2">
-        <v>643</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N214" s="2"/>
+      <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
         <v>73</v>
       </c>
@@ -24570,7 +24594,7 @@
         <v>73</v>
       </c>
       <c r="S214" t="s" s="2">
-        <v>73</v>
+        <v>673</v>
       </c>
       <c r="T214" t="s" s="2">
         <v>73</v>
@@ -24585,13 +24609,11 @@
         <v>73</v>
       </c>
       <c r="X214" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="Y214" t="s" s="2">
-        <v>644</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="Y214" s="2"/>
       <c r="Z214" t="s" s="2">
-        <v>645</v>
+        <v>674</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>73</v>
@@ -24609,7 +24631,7 @@
         <v>73</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>646</v>
+        <v>215</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>74</v>
@@ -24629,9 +24651,11 @@
         <v>675</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="C215" s="2"/>
+        <v>621</v>
+      </c>
+      <c r="C215" t="s" s="2">
+        <v>676</v>
+      </c>
       <c r="D215" t="s" s="2">
         <v>73</v>
       </c>
@@ -24643,26 +24667,24 @@
         <v>81</v>
       </c>
       <c r="H215" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I215" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J215" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>648</v>
+        <v>677</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>649</v>
+        <v>678</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="N215" t="s" s="2">
-        <v>651</v>
-      </c>
+        <v>679</v>
+      </c>
+      <c r="N215" s="2"/>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>73</v>
@@ -24711,27 +24733,27 @@
         <v>73</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>652</v>
+        <v>109</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH215" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI215" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>653</v>
+        <v>626</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24739,7 +24761,7 @@
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G216" t="s" s="2">
         <v>81</v>
@@ -24754,16 +24776,16 @@
         <v>82</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>655</v>
+        <v>628</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>314</v>
+        <v>379</v>
       </c>
       <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
@@ -24774,7 +24796,7 @@
         <v>73</v>
       </c>
       <c r="S216" t="s" s="2">
-        <v>73</v>
+        <v>681</v>
       </c>
       <c r="T216" t="s" s="2">
         <v>73</v>
@@ -24789,13 +24811,13 @@
         <v>73</v>
       </c>
       <c r="X216" t="s" s="2">
-        <v>73</v>
+        <v>285</v>
       </c>
       <c r="Y216" t="s" s="2">
-        <v>73</v>
+        <v>629</v>
       </c>
       <c r="Z216" t="s" s="2">
-        <v>73</v>
+        <v>630</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>73</v>
@@ -24813,7 +24835,7 @@
         <v>73</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>656</v>
+        <v>631</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>74</v>
@@ -24822,18 +24844,18 @@
         <v>81</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>93</v>
+        <v>632</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>316</v>
+        <v>94</v>
       </c>
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>677</v>
+        <v>633</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24841,10 +24863,10 @@
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G217" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H217" t="s" s="2">
         <v>82</v>
@@ -24853,22 +24875,22 @@
         <v>73</v>
       </c>
       <c r="J217" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>678</v>
+        <v>96</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>680</v>
+        <v>635</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>681</v>
+        <v>636</v>
       </c>
       <c r="O217" t="s" s="2">
-        <v>682</v>
+        <v>637</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>73</v>
@@ -24917,19 +24939,19 @@
         <v>73</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>677</v>
+        <v>638</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH217" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI217" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>683</v>
+        <v>94</v>
       </c>
     </row>
     <row r="218" hidden="true">
@@ -24937,7 +24959,7 @@
         <v>684</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>684</v>
+        <v>639</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -24954,25 +24976,25 @@
         <v>73</v>
       </c>
       <c r="I218" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J218" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K218" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L218" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="M218" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="N218" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="L218" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="M218" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="N218" t="s" s="2">
-        <v>688</v>
-      </c>
       <c r="O218" t="s" s="2">
-        <v>689</v>
+        <v>643</v>
       </c>
       <c r="P218" t="s" s="2">
         <v>73</v>
@@ -24997,13 +25019,13 @@
         <v>73</v>
       </c>
       <c r="X218" t="s" s="2">
-        <v>73</v>
+        <v>285</v>
       </c>
       <c r="Y218" t="s" s="2">
-        <v>73</v>
+        <v>644</v>
       </c>
       <c r="Z218" t="s" s="2">
-        <v>73</v>
+        <v>645</v>
       </c>
       <c r="AA218" t="s" s="2">
         <v>73</v>
@@ -25021,7 +25043,7 @@
         <v>73</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>684</v>
+        <v>646</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>74</v>
@@ -25033,15 +25055,15 @@
         <v>93</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>323</v>
+        <v>94</v>
       </c>
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>690</v>
+        <v>647</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -25061,18 +25083,20 @@
         <v>73</v>
       </c>
       <c r="J219" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>96</v>
+        <v>648</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>97</v>
+        <v>649</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N219" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="N219" t="s" s="2">
+        <v>651</v>
+      </c>
       <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
         <v>73</v>
@@ -25121,7 +25145,7 @@
         <v>73</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>99</v>
+        <v>652</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>74</v>
@@ -25130,29 +25154,29 @@
         <v>81</v>
       </c>
       <c r="AI219" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>691</v>
+        <v>653</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E220" s="2"/>
       <c r="F220" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G220" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H220" t="s" s="2">
         <v>73</v>
@@ -25161,19 +25185,19 @@
         <v>73</v>
       </c>
       <c r="J220" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>103</v>
+        <v>654</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>104</v>
+        <v>655</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>105</v>
+        <v>314</v>
       </c>
       <c r="O220" s="2"/>
       <c r="P220" t="s" s="2">
@@ -25211,39 +25235,39 @@
         <v>73</v>
       </c>
       <c r="AB220" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC220" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD220" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE220" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>109</v>
+        <v>656</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH220" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI220" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>110</v>
+        <v>316</v>
       </c>
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -25254,30 +25278,32 @@
         <v>74</v>
       </c>
       <c r="G221" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H221" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I221" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J221" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="L221" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="M221" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N221" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="O221" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="M221" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="N221" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="O221" s="2"/>
       <c r="P221" t="s" s="2">
         <v>73</v>
       </c>
@@ -25325,27 +25351,27 @@
         <v>73</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH221" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI221" t="s" s="2">
-        <v>697</v>
+        <v>93</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>94</v>
+        <v>694</v>
       </c>
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -25368,18 +25394,20 @@
         <v>82</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>128</v>
+        <v>696</v>
       </c>
       <c r="L222" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="M222" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="N222" t="s" s="2">
         <v>699</v>
       </c>
-      <c r="M222" t="s" s="2">
+      <c r="O222" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="N222" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="O222" s="2"/>
       <c r="P222" t="s" s="2">
         <v>73</v>
       </c>
@@ -25403,13 +25431,13 @@
         <v>73</v>
       </c>
       <c r="X222" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="Y222" t="s" s="2">
-        <v>702</v>
+        <v>73</v>
       </c>
       <c r="Z222" t="s" s="2">
-        <v>474</v>
+        <v>73</v>
       </c>
       <c r="AA222" t="s" s="2">
         <v>73</v>
@@ -25427,7 +25455,7 @@
         <v>73</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>74</v>
@@ -25439,15 +25467,15 @@
         <v>93</v>
       </c>
       <c r="AJ222" t="s" s="2">
-        <v>94</v>
+        <v>323</v>
       </c>
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -25467,20 +25495,18 @@
         <v>73</v>
       </c>
       <c r="J223" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>271</v>
+        <v>96</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>705</v>
+        <v>97</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="N223" t="s" s="2">
-        <v>707</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N223" s="2"/>
       <c r="O223" s="2"/>
       <c r="P223" t="s" s="2">
         <v>73</v>
@@ -25529,7 +25555,7 @@
         <v>73</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>708</v>
+        <v>99</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>74</v>
@@ -25538,29 +25564,29 @@
         <v>81</v>
       </c>
       <c r="AI223" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ223" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G224" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H224" t="s" s="2">
         <v>73</v>
@@ -25569,19 +25595,19 @@
         <v>73</v>
       </c>
       <c r="J224" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>710</v>
+        <v>103</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>711</v>
+        <v>104</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>712</v>
+        <v>105</v>
       </c>
       <c r="O224" s="2"/>
       <c r="P224" t="s" s="2">
@@ -25619,39 +25645,39 @@
         <v>73</v>
       </c>
       <c r="AB224" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC224" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD224" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE224" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>713</v>
+        <v>109</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH224" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI224" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ224" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -25662,7 +25688,7 @@
         <v>74</v>
       </c>
       <c r="G225" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H225" t="s" s="2">
         <v>73</v>
@@ -25671,23 +25697,21 @@
         <v>73</v>
       </c>
       <c r="J225" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>715</v>
+        <v>96</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="O225" t="s" s="2">
-        <v>719</v>
-      </c>
+        <v>706</v>
+      </c>
+      <c r="O225" s="2"/>
       <c r="P225" t="s" s="2">
         <v>73</v>
       </c>
@@ -25735,16 +25759,16 @@
         <v>73</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH225" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI225" t="s" s="2">
-        <v>93</v>
+        <v>708</v>
       </c>
       <c r="AJ225" t="s" s="2">
         <v>94</v>
@@ -25752,10 +25776,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -25775,18 +25799,20 @@
         <v>73</v>
       </c>
       <c r="J226" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>97</v>
+        <v>710</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N226" s="2"/>
+        <v>711</v>
+      </c>
+      <c r="N226" t="s" s="2">
+        <v>712</v>
+      </c>
       <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
         <v>73</v>
@@ -25811,13 +25837,13 @@
         <v>73</v>
       </c>
       <c r="X226" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Y226" t="s" s="2">
-        <v>73</v>
+        <v>713</v>
       </c>
       <c r="Z226" t="s" s="2">
-        <v>73</v>
+        <v>474</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>73</v>
@@ -25835,7 +25861,7 @@
         <v>73</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>99</v>
+        <v>714</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>74</v>
@@ -25844,29 +25870,29 @@
         <v>81</v>
       </c>
       <c r="AI226" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ226" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E227" s="2"/>
       <c r="F227" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G227" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H227" t="s" s="2">
         <v>73</v>
@@ -25875,19 +25901,19 @@
         <v>73</v>
       </c>
       <c r="J227" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>102</v>
+        <v>271</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>103</v>
+        <v>716</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>104</v>
+        <v>717</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>105</v>
+        <v>718</v>
       </c>
       <c r="O227" s="2"/>
       <c r="P227" t="s" s="2">
@@ -25925,75 +25951,73 @@
         <v>73</v>
       </c>
       <c r="AB227" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC227" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD227" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE227" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>109</v>
+        <v>719</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH227" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI227" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ227" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
-        <v>723</v>
+        <v>73</v>
       </c>
       <c r="E228" s="2"/>
       <c r="F228" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G228" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H228" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I228" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J228" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O228" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>723</v>
+      </c>
+      <c r="O228" s="2"/>
       <c r="P228" t="s" s="2">
         <v>73</v>
       </c>
@@ -26041,27 +26065,27 @@
         <v>73</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH228" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI228" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ228" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -26072,7 +26096,7 @@
         <v>74</v>
       </c>
       <c r="G229" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H229" t="s" s="2">
         <v>73</v>
@@ -26084,19 +26108,19 @@
         <v>73</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>290</v>
+        <v>726</v>
       </c>
       <c r="L229" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="M229" t="s" s="2">
         <v>728</v>
       </c>
-      <c r="M229" t="s" s="2">
+      <c r="N229" t="s" s="2">
         <v>729</v>
       </c>
-      <c r="N229" t="s" s="2">
+      <c r="O229" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="O229" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="P229" t="s" s="2">
         <v>73</v>
@@ -26121,13 +26145,13 @@
         <v>73</v>
       </c>
       <c r="X229" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="Y229" t="s" s="2">
-        <v>732</v>
+        <v>73</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>733</v>
+        <v>73</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>73</v>
@@ -26145,13 +26169,13 @@
         <v>73</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH229" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI229" t="s" s="2">
         <v>93</v>
@@ -26162,10 +26186,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -26188,20 +26212,16 @@
         <v>73</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>735</v>
+        <v>96</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>736</v>
+        <v>97</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="N230" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="O230" t="s" s="2">
-        <v>739</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N230" s="2"/>
+      <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
         <v>73</v>
       </c>
@@ -26249,7 +26269,7 @@
         <v>73</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>734</v>
+        <v>99</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>74</v>
@@ -26258,22 +26278,22 @@
         <v>81</v>
       </c>
       <c r="AI230" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ230" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" t="s" s="2">
@@ -26292,18 +26312,18 @@
         <v>73</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>612</v>
+        <v>102</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>741</v>
+        <v>103</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="N231" s="2"/>
-      <c r="O231" t="s" s="2">
-        <v>742</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N231" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="O231" s="2"/>
       <c r="P231" t="s" s="2">
         <v>73</v>
       </c>
@@ -26339,19 +26359,19 @@
         <v>73</v>
       </c>
       <c r="AB231" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC231" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD231" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE231" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>740</v>
+        <v>109</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>74</v>
@@ -26363,50 +26383,50 @@
         <v>93</v>
       </c>
       <c r="AJ231" t="s" s="2">
-        <v>743</v>
+        <v>110</v>
       </c>
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
-        <v>73</v>
+        <v>734</v>
       </c>
       <c r="E232" s="2"/>
       <c r="F232" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G232" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H232" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I232" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J232" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>745</v>
+        <v>102</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>680</v>
+        <v>736</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>681</v>
+        <v>105</v>
       </c>
       <c r="O232" t="s" s="2">
-        <v>747</v>
+        <v>268</v>
       </c>
       <c r="P232" t="s" s="2">
         <v>73</v>
@@ -26455,27 +26475,27 @@
         <v>73</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH232" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI232" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ232" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -26486,10 +26506,10 @@
         <v>74</v>
       </c>
       <c r="G233" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H233" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I233" t="s" s="2">
         <v>73</v>
@@ -26498,19 +26518,19 @@
         <v>73</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>749</v>
+        <v>290</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>688</v>
+        <v>741</v>
       </c>
       <c r="O233" t="s" s="2">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>73</v>
@@ -26535,13 +26555,13 @@
         <v>73</v>
       </c>
       <c r="X233" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Y233" t="s" s="2">
-        <v>73</v>
+        <v>743</v>
       </c>
       <c r="Z233" t="s" s="2">
-        <v>73</v>
+        <v>744</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>73</v>
@@ -26559,23 +26579,437 @@
         <v>73</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH233" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI233" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ233" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="234" hidden="true">
+      <c r="A234" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="C234" s="2"/>
+      <c r="D234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E234" s="2"/>
+      <c r="F234" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G234" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K234" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="L234" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="M234" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="N234" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="O234" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="P234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q234" s="2"/>
+      <c r="R234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE234" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF234" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="AG234" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH234" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI234" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ234" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="235" hidden="true">
+      <c r="A235" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="B235" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="C235" s="2"/>
+      <c r="D235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E235" s="2"/>
+      <c r="F235" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G235" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K235" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="L235" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="M235" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="N235" s="2"/>
+      <c r="O235" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="P235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q235" s="2"/>
+      <c r="R235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE235" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF235" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="AG235" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH235" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI235" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ235" t="s" s="2">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="236" hidden="true">
+      <c r="A236" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="B236" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="C236" s="2"/>
+      <c r="D236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E236" s="2"/>
+      <c r="F236" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G236" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K236" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="L236" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="M236" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N236" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="O236" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="P236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q236" s="2"/>
+      <c r="R236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE236" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF236" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="AG236" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH236" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI236" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ236" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="237" hidden="true">
+      <c r="A237" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="C237" s="2"/>
+      <c r="D237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E237" s="2"/>
+      <c r="F237" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K237" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="L237" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="M237" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="N237" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="O237" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="P237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q237" s="2"/>
+      <c r="R237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE237" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF237" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="AG237" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI237" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ237" t="s" s="2">
         <v>323</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ233">
+  <autoFilter ref="A1:AJ237">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -26585,7 +27019,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI232">
+  <conditionalFormatting sqref="A2:AI236">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$237</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$224</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7661" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7248" uniqueCount="737">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T10:45:14+00:00</t>
+    <t>2024-03-07T10:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2070,91 +2070,6 @@
   </si>
   <si>
     <t>Les BALs MSS de type ORG ou APP rattachées à une personne morale responsable de l’accès et de l’usage de la BAL (boiteLettreMSS).</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType.url</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.url</t>
-  </si>
-  <si>
-    <t>http://interopsante.org/fhir/StructureDefinition/FrContactPointEmailType</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.value[x]</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
-  &lt;code value="MSSANTE"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>http://interopsante.org/fhir/ValueSet/fr-email-type</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t>as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata}
-</t>
-  </si>
-  <si>
-    <t>Les attributs 'responsible' et 'phone' ne sont pas disponibles en accès libre.</t>
-  </si>
-  <si>
-    <t>Extension contenant les métadonnées de la mailbox mss.</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.system</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.value</t>
-  </si>
-  <si>
-    <t>Boîte Aux Lettres (BAL) MSS</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.use</t>
-  </si>
-  <si>
-    <t>Applications can assume that a contact is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.rank</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.period</t>
   </si>
   <si>
     <t>Organization.address</t>
@@ -2714,7 +2629,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ237"/>
+  <dimension ref="A1:AJ224"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="80.17578125" customWidth="true" bestFit="true"/>
@@ -23947,7 +23862,7 @@
         <v>661</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>620</v>
+        <v>661</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23958,10 +23873,10 @@
         <v>74</v>
       </c>
       <c r="G208" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H208" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I208" t="s" s="2">
         <v>73</v>
@@ -23970,16 +23885,20 @@
         <v>73</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>96</v>
+        <v>662</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>97</v>
+        <v>663</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N208" s="2"/>
-      <c r="O208" s="2"/>
+        <v>664</v>
+      </c>
+      <c r="N208" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="O208" t="s" s="2">
+        <v>666</v>
+      </c>
       <c r="P208" t="s" s="2">
         <v>73</v>
       </c>
@@ -24027,38 +23946,38 @@
         <v>73</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>99</v>
+        <v>661</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH208" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI208" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>73</v>
+        <v>667</v>
       </c>
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>621</v>
+        <v>668</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>73</v>
@@ -24067,21 +23986,23 @@
         <v>73</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>102</v>
+        <v>669</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>103</v>
+        <v>670</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>104</v>
+        <v>671</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O209" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="O209" t="s" s="2">
+        <v>673</v>
+      </c>
       <c r="P209" t="s" s="2">
         <v>73</v>
       </c>
@@ -24117,43 +24038,41 @@
         <v>73</v>
       </c>
       <c r="AB209" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC209" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD209" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE209" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>109</v>
+        <v>668</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI209" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>110</v>
+        <v>323</v>
       </c>
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C210" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
         <v>73</v>
       </c>
@@ -24174,13 +24093,13 @@
         <v>73</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>624</v>
+        <v>96</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>625</v>
+        <v>97</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>191</v>
+        <v>98</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
@@ -24231,38 +24150,38 @@
         <v>73</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH210" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI210" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>73</v>
@@ -24274,15 +24193,17 @@
         <v>73</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N211" s="2"/>
+        <v>104</v>
+      </c>
+      <c r="N211" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
         <v>73</v>
@@ -24319,39 +24240,39 @@
         <v>73</v>
       </c>
       <c r="AB211" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC211" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD211" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE211" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI211" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -24362,7 +24283,7 @@
         <v>74</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H212" t="s" s="2">
         <v>73</v>
@@ -24371,18 +24292,20 @@
         <v>73</v>
       </c>
       <c r="J212" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>479</v>
+        <v>677</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N212" s="2"/>
+        <v>678</v>
+      </c>
+      <c r="N212" t="s" s="2">
+        <v>679</v>
+      </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>73</v>
@@ -24419,39 +24342,39 @@
         <v>73</v>
       </c>
       <c r="AB212" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC212" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD212" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE212" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>109</v>
+        <v>680</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI212" t="s" s="2">
-        <v>93</v>
+        <v>681</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>668</v>
+        <v>682</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>669</v>
+        <v>682</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -24459,7 +24382,7 @@
       </c>
       <c r="E213" s="2"/>
       <c r="F213" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G213" t="s" s="2">
         <v>81</v>
@@ -24471,19 +24394,19 @@
         <v>73</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K213" t="s" s="2">
         <v>128</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>205</v>
+        <v>683</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>206</v>
+        <v>684</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>207</v>
+        <v>685</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
@@ -24491,7 +24414,7 @@
       </c>
       <c r="Q213" s="2"/>
       <c r="R213" t="s" s="2">
-        <v>670</v>
+        <v>73</v>
       </c>
       <c r="S213" t="s" s="2">
         <v>73</v>
@@ -24509,13 +24432,13 @@
         <v>73</v>
       </c>
       <c r="X213" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>73</v>
+        <v>686</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>73</v>
+        <v>474</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>73</v>
@@ -24533,27 +24456,27 @@
         <v>73</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>209</v>
+        <v>687</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AH213" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI213" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>671</v>
+        <v>688</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>672</v>
+        <v>688</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -24573,18 +24496,20 @@
         <v>73</v>
       </c>
       <c r="J214" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>140</v>
+        <v>271</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>213</v>
+        <v>689</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N214" s="2"/>
+        <v>690</v>
+      </c>
+      <c r="N214" t="s" s="2">
+        <v>691</v>
+      </c>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
         <v>73</v>
@@ -24594,7 +24519,7 @@
         <v>73</v>
       </c>
       <c r="S214" t="s" s="2">
-        <v>673</v>
+        <v>73</v>
       </c>
       <c r="T214" t="s" s="2">
         <v>73</v>
@@ -24609,11 +24534,13 @@
         <v>73</v>
       </c>
       <c r="X214" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y214" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Y214" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="Z214" t="s" s="2">
-        <v>674</v>
+        <v>73</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>73</v>
@@ -24631,7 +24558,7 @@
         <v>73</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>215</v>
+        <v>692</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>74</v>
@@ -24648,14 +24575,12 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C215" t="s" s="2">
-        <v>676</v>
-      </c>
+        <v>693</v>
+      </c>
+      <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
         <v>73</v>
       </c>
@@ -24667,24 +24592,26 @@
         <v>81</v>
       </c>
       <c r="H215" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I215" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J215" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I215" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J215" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K215" t="s" s="2">
-        <v>677</v>
+        <v>96</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>678</v>
+        <v>694</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="N215" s="2"/>
+        <v>695</v>
+      </c>
+      <c r="N215" t="s" s="2">
+        <v>696</v>
+      </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>73</v>
@@ -24733,27 +24660,27 @@
         <v>73</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>109</v>
+        <v>697</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH215" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI215" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>680</v>
+        <v>698</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>626</v>
+        <v>698</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24761,10 +24688,10 @@
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>73</v>
@@ -24773,21 +24700,23 @@
         <v>73</v>
       </c>
       <c r="J216" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>162</v>
+        <v>699</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>627</v>
+        <v>700</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>628</v>
+        <v>701</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O216" s="2"/>
+        <v>702</v>
+      </c>
+      <c r="O216" t="s" s="2">
+        <v>703</v>
+      </c>
       <c r="P216" t="s" s="2">
         <v>73</v>
       </c>
@@ -24796,7 +24725,7 @@
         <v>73</v>
       </c>
       <c r="S216" t="s" s="2">
-        <v>681</v>
+        <v>73</v>
       </c>
       <c r="T216" t="s" s="2">
         <v>73</v>
@@ -24811,13 +24740,13 @@
         <v>73</v>
       </c>
       <c r="X216" t="s" s="2">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="Y216" t="s" s="2">
-        <v>629</v>
+        <v>73</v>
       </c>
       <c r="Z216" t="s" s="2">
-        <v>630</v>
+        <v>73</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>73</v>
@@ -24835,16 +24764,16 @@
         <v>73</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>631</v>
+        <v>698</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH216" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>632</v>
+        <v>93</v>
       </c>
       <c r="AJ216" t="s" s="2">
         <v>94</v>
@@ -24852,10 +24781,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>682</v>
+        <v>704</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>633</v>
+        <v>704</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24863,35 +24792,31 @@
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G217" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H217" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I217" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J217" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K217" t="s" s="2">
         <v>96</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>683</v>
+        <v>97</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N217" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O217" t="s" s="2">
-        <v>637</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N217" s="2"/>
+      <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
         <v>73</v>
       </c>
@@ -24939,7 +24864,7 @@
         <v>73</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>638</v>
+        <v>99</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>74</v>
@@ -24948,54 +24873,52 @@
         <v>81</v>
       </c>
       <c r="AI217" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>684</v>
+        <v>705</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>639</v>
+        <v>705</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E218" s="2"/>
       <c r="F218" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G218" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H218" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I218" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J218" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>640</v>
+        <v>103</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>641</v>
+        <v>104</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="O218" t="s" s="2">
-        <v>643</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="O218" s="2"/>
       <c r="P218" t="s" s="2">
         <v>73</v>
       </c>
@@ -25019,85 +24942,87 @@
         <v>73</v>
       </c>
       <c r="X218" t="s" s="2">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="Y218" t="s" s="2">
-        <v>644</v>
+        <v>73</v>
       </c>
       <c r="Z218" t="s" s="2">
-        <v>645</v>
+        <v>73</v>
       </c>
       <c r="AA218" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB218" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC218" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD218" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE218" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>646</v>
+        <v>109</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH218" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI218" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>686</v>
+        <v>706</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>647</v>
+        <v>706</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
-        <v>73</v>
+        <v>707</v>
       </c>
       <c r="E219" s="2"/>
       <c r="F219" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G219" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H219" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I219" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J219" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>648</v>
+        <v>102</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>649</v>
+        <v>708</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>650</v>
+        <v>709</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="O219" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="O219" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="P219" t="s" s="2">
         <v>73</v>
       </c>
@@ -25145,27 +25070,27 @@
         <v>73</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>652</v>
+        <v>710</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH219" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI219" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>687</v>
+        <v>711</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>653</v>
+        <v>711</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -25185,21 +25110,23 @@
         <v>73</v>
       </c>
       <c r="J220" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>212</v>
+        <v>290</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>654</v>
+        <v>712</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>655</v>
+        <v>713</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O220" s="2"/>
+        <v>714</v>
+      </c>
+      <c r="O220" t="s" s="2">
+        <v>715</v>
+      </c>
       <c r="P220" t="s" s="2">
         <v>73</v>
       </c>
@@ -25223,13 +25150,13 @@
         <v>73</v>
       </c>
       <c r="X220" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Y220" t="s" s="2">
-        <v>73</v>
+        <v>716</v>
       </c>
       <c r="Z220" t="s" s="2">
-        <v>73</v>
+        <v>717</v>
       </c>
       <c r="AA220" t="s" s="2">
         <v>73</v>
@@ -25247,7 +25174,7 @@
         <v>73</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>656</v>
+        <v>711</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>74</v>
@@ -25259,15 +25186,15 @@
         <v>93</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>316</v>
+        <v>94</v>
       </c>
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>688</v>
+        <v>718</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>688</v>
+        <v>718</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -25278,10 +25205,10 @@
         <v>74</v>
       </c>
       <c r="G221" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H221" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I221" t="s" s="2">
         <v>73</v>
@@ -25290,19 +25217,19 @@
         <v>73</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>689</v>
+        <v>719</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>690</v>
+        <v>720</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>691</v>
+        <v>721</v>
       </c>
       <c r="N221" t="s" s="2">
-        <v>692</v>
+        <v>722</v>
       </c>
       <c r="O221" t="s" s="2">
-        <v>693</v>
+        <v>723</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>73</v>
@@ -25351,27 +25278,27 @@
         <v>73</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>688</v>
+        <v>718</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH221" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI221" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>694</v>
+        <v>94</v>
       </c>
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -25382,7 +25309,7 @@
         <v>74</v>
       </c>
       <c r="G222" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H222" t="s" s="2">
         <v>73</v>
@@ -25391,22 +25318,20 @@
         <v>73</v>
       </c>
       <c r="J222" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>696</v>
+        <v>612</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>697</v>
+        <v>725</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="N222" t="s" s="2">
-        <v>699</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>700</v>
+        <v>726</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>73</v>
@@ -25455,27 +25380,27 @@
         <v>73</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH222" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI222" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ222" t="s" s="2">
-        <v>323</v>
+        <v>727</v>
       </c>
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>701</v>
+        <v>728</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>701</v>
+        <v>728</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -25498,16 +25423,20 @@
         <v>73</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>96</v>
+        <v>729</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>97</v>
+        <v>730</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N223" s="2"/>
-      <c r="O223" s="2"/>
+        <v>664</v>
+      </c>
+      <c r="N223" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="O223" t="s" s="2">
+        <v>731</v>
+      </c>
       <c r="P223" t="s" s="2">
         <v>73</v>
       </c>
@@ -25555,7 +25484,7 @@
         <v>73</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>99</v>
+        <v>728</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>74</v>
@@ -25564,22 +25493,22 @@
         <v>81</v>
       </c>
       <c r="AI223" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ223" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>702</v>
+        <v>732</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>702</v>
+        <v>732</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" t="s" s="2">
@@ -25589,7 +25518,7 @@
         <v>75</v>
       </c>
       <c r="H224" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I224" t="s" s="2">
         <v>73</v>
@@ -25598,18 +25527,20 @@
         <v>73</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>102</v>
+        <v>733</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>103</v>
+        <v>734</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>104</v>
+        <v>735</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O224" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="O224" t="s" s="2">
+        <v>736</v>
+      </c>
       <c r="P224" t="s" s="2">
         <v>73</v>
       </c>
@@ -25645,19 +25576,19 @@
         <v>73</v>
       </c>
       <c r="AB224" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC224" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD224" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE224" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>109</v>
+        <v>732</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>74</v>
@@ -25669,1347 +25600,11 @@
         <v>93</v>
       </c>
       <c r="AJ224" t="s" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="225" hidden="true">
-      <c r="A225" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="B225" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="C225" s="2"/>
-      <c r="D225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E225" s="2"/>
-      <c r="F225" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G225" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J225" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K225" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L225" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="M225" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="N225" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="O225" s="2"/>
-      <c r="P225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q225" s="2"/>
-      <c r="R225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF225" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="AG225" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH225" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI225" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="AJ225" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="226" hidden="true">
-      <c r="A226" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="B226" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="C226" s="2"/>
-      <c r="D226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E226" s="2"/>
-      <c r="F226" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G226" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J226" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K226" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="L226" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="M226" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="N226" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="O226" s="2"/>
-      <c r="P226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q226" s="2"/>
-      <c r="R226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X226" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y226" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="Z226" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AA226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF226" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="AG226" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH226" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI226" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ226" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="227" hidden="true">
-      <c r="A227" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="B227" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="C227" s="2"/>
-      <c r="D227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E227" s="2"/>
-      <c r="F227" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G227" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J227" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K227" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="L227" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="M227" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="N227" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="O227" s="2"/>
-      <c r="P227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q227" s="2"/>
-      <c r="R227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF227" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="AG227" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH227" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI227" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ227" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="228" hidden="true">
-      <c r="A228" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="B228" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="C228" s="2"/>
-      <c r="D228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E228" s="2"/>
-      <c r="F228" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G228" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J228" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K228" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L228" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="M228" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="N228" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="O228" s="2"/>
-      <c r="P228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q228" s="2"/>
-      <c r="R228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF228" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="AG228" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH228" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI228" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ228" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="229" hidden="true">
-      <c r="A229" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="B229" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="C229" s="2"/>
-      <c r="D229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E229" s="2"/>
-      <c r="F229" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G229" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K229" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="L229" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="M229" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="N229" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="O229" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="P229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q229" s="2"/>
-      <c r="R229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF229" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="AG229" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH229" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI229" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ229" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="230" hidden="true">
-      <c r="A230" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="B230" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C230" s="2"/>
-      <c r="D230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E230" s="2"/>
-      <c r="F230" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G230" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K230" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L230" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="M230" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N230" s="2"/>
-      <c r="O230" s="2"/>
-      <c r="P230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q230" s="2"/>
-      <c r="R230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF230" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AG230" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH230" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ230" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="231" hidden="true">
-      <c r="A231" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="B231" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="C231" s="2"/>
-      <c r="D231" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="E231" s="2"/>
-      <c r="F231" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G231" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K231" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L231" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M231" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N231" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O231" s="2"/>
-      <c r="P231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q231" s="2"/>
-      <c r="R231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB231" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AC231" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AD231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE231" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AF231" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG231" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH231" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI231" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ231" t="s" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="232" hidden="true">
-      <c r="A232" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="B232" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="C232" s="2"/>
-      <c r="D232" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="E232" s="2"/>
-      <c r="F232" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G232" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I232" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J232" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K232" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L232" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="M232" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="N232" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O232" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="P232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q232" s="2"/>
-      <c r="R232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF232" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="AG232" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH232" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI232" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ232" t="s" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="233" hidden="true">
-      <c r="A233" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="B233" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="C233" s="2"/>
-      <c r="D233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E233" s="2"/>
-      <c r="F233" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G233" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K233" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="L233" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="M233" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="N233" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="O233" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="P233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q233" s="2"/>
-      <c r="R233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X233" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y233" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="Z233" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="AA233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF233" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="AG233" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH233" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI233" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ233" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="234" hidden="true">
-      <c r="A234" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="B234" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="C234" s="2"/>
-      <c r="D234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E234" s="2"/>
-      <c r="F234" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G234" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K234" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="L234" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="M234" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="N234" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="O234" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="P234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q234" s="2"/>
-      <c r="R234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE234" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF234" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="AG234" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH234" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI234" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ234" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="235" hidden="true">
-      <c r="A235" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="B235" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="C235" s="2"/>
-      <c r="D235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E235" s="2"/>
-      <c r="F235" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G235" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K235" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="L235" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="M235" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="N235" s="2"/>
-      <c r="O235" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="P235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q235" s="2"/>
-      <c r="R235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE235" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF235" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="AG235" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH235" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI235" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ235" t="s" s="2">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="236" hidden="true">
-      <c r="A236" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="B236" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="C236" s="2"/>
-      <c r="D236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E236" s="2"/>
-      <c r="F236" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G236" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K236" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="L236" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="M236" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N236" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="P236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q236" s="2"/>
-      <c r="R236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE236" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF236" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="AG236" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH236" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI236" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ236" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="237" hidden="true">
-      <c r="A237" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="B237" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="C237" s="2"/>
-      <c r="D237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E237" s="2"/>
-      <c r="F237" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G237" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H237" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K237" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="L237" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="M237" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="N237" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="O237" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="P237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q237" s="2"/>
-      <c r="R237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE237" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF237" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="AG237" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH237" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI237" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ237" t="s" s="2">
         <v>323</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ237">
+  <autoFilter ref="A1:AJ224">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -27019,7 +25614,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI236">
+  <conditionalFormatting sqref="A2:AI223">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T08:21:45+00:00</t>
+    <t>2024-03-13T15:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8077" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8078" uniqueCount="821">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-09T07:46:55+00:00</t>
+    <t>2024-04-10T12:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -689,6 +689,9 @@
 </t>
   </si>
   <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
     <t>The date range that this organization should be considered available.</t>
   </si>
   <si>
@@ -738,7 +741,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -778,8 +781,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>dateCreation</t>
@@ -1743,9 +1746,6 @@
   </si>
   <si>
     <t>Organization.type.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-organization-types</t>
@@ -5413,10 +5413,10 @@
         <v>214</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5488,7 +5488,7 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5614,14 +5614,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5643,12 +5643,14 @@
         <v>110</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -5706,7 +5708,7 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>118</v>
@@ -5718,7 +5720,7 @@
         <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -5729,10 +5731,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5758,13 +5760,13 @@
         <v>136</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5772,7 +5774,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>78</v>
@@ -5814,7 +5816,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>89</v>
@@ -5846,10 +5848,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5872,13 +5874,13 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5929,7 +5931,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5938,7 +5940,7 @@
         <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>101</v>
@@ -5961,10 +5963,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6076,10 +6078,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6170,7 +6172,7 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>118</v>
@@ -6182,7 +6184,7 @@
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -6193,10 +6195,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6219,16 +6221,16 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6278,7 +6280,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -6287,19 +6289,19 @@
         <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -6310,10 +6312,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6336,23 +6338,23 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>78</v>
@@ -6397,7 +6399,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -6406,19 +6408,19 @@
         <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -6429,13 +6431,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>78</v>
@@ -6457,13 +6459,13 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6546,13 +6548,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>78</v>
@@ -6574,13 +6576,13 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6646,7 +6648,7 @@
         <v>118</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>78</v>
@@ -6663,13 +6665,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>78</v>
@@ -6691,13 +6693,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6780,13 +6782,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>78</v>
@@ -6808,13 +6810,13 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6880,7 +6882,7 @@
         <v>118</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>78</v>
@@ -6897,13 +6899,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>78</v>
@@ -6925,13 +6927,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7014,13 +7016,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>78</v>
@@ -7042,13 +7044,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7131,10 +7133,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7160,16 +7162,16 @@
         <v>110</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -7218,7 +7220,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -7250,10 +7252,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7276,17 +7278,17 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -7323,10 +7325,10 @@
         <v>78</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>78</v>
@@ -7335,7 +7337,7 @@
         <v>116</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -7344,7 +7346,7 @@
         <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>101</v>
@@ -7353,27 +7355,27 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>78</v>
@@ -7395,17 +7397,17 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -7454,7 +7456,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7463,33 +7465,33 @@
         <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7601,10 +7603,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7718,10 +7720,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7747,16 +7749,16 @@
         <v>175</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7766,7 +7768,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7781,13 +7783,13 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -7805,7 +7807,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7826,7 +7828,7 @@
         <v>198</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -7837,10 +7839,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7863,19 +7865,19 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -7885,7 +7887,7 @@
         <v>78</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>78</v>
@@ -7903,10 +7905,10 @@
         <v>157</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
@@ -7924,7 +7926,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7942,10 +7944,10 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -7956,10 +7958,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7985,16 +7987,16 @@
         <v>136</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -8004,10 +8006,10 @@
         <v>78</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>78</v>
@@ -8043,7 +8045,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -8061,13 +8063,13 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -8075,10 +8077,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8104,13 +8106,13 @@
         <v>103</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8124,7 +8126,7 @@
         <v>78</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>78</v>
@@ -8160,7 +8162,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -8178,13 +8180,13 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>78</v>
@@ -8192,10 +8194,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8218,13 +8220,13 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8275,7 +8277,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -8293,13 +8295,13 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -8307,10 +8309,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8333,16 +8335,16 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8392,7 +8394,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8410,13 +8412,13 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
@@ -8424,13 +8426,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>78</v>
@@ -8452,17 +8454,17 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -8511,7 +8513,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8520,33 +8522,33 @@
         <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8658,10 +8660,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8775,10 +8777,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8804,16 +8806,16 @@
         <v>175</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -8838,13 +8840,13 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -8862,7 +8864,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8883,7 +8885,7 @@
         <v>198</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -8894,10 +8896,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8920,19 +8922,19 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -8960,10 +8962,10 @@
         <v>157</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -8981,7 +8983,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8999,10 +9001,10 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -9013,10 +9015,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9128,10 +9130,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9245,10 +9247,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9274,16 +9276,16 @@
         <v>153</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -9332,7 +9334,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9350,10 +9352,10 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -9364,10 +9366,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9479,10 +9481,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9596,10 +9598,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9625,16 +9627,16 @@
         <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -9644,7 +9646,7 @@
         <v>78</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>78</v>
@@ -9683,7 +9685,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9701,10 +9703,10 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -9715,10 +9717,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9744,13 +9746,13 @@
         <v>103</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9800,7 +9802,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9818,10 +9820,10 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -9832,10 +9834,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9861,14 +9863,14 @@
         <v>175</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9917,7 +9919,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9935,10 +9937,10 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -9949,10 +9951,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9978,14 +9980,14 @@
         <v>103</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -10034,7 +10036,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -10052,10 +10054,10 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -10066,10 +10068,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10092,19 +10094,19 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
@@ -10153,7 +10155,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -10171,10 +10173,10 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -10185,10 +10187,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10214,16 +10216,16 @@
         <v>103</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -10272,7 +10274,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -10290,10 +10292,10 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -10304,10 +10306,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10333,16 +10335,16 @@
         <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -10352,10 +10354,10 @@
         <v>78</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>78</v>
@@ -10391,7 +10393,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10409,13 +10411,13 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -10423,10 +10425,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10452,13 +10454,13 @@
         <v>103</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10472,7 +10474,7 @@
         <v>78</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>78</v>
@@ -10508,7 +10510,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10526,13 +10528,13 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -10540,10 +10542,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10566,13 +10568,13 @@
         <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10623,7 +10625,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10641,13 +10643,13 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -10655,10 +10657,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10681,16 +10683,16 @@
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10740,7 +10742,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10758,13 +10760,13 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -10772,13 +10774,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>78</v>
@@ -10800,17 +10802,17 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10859,7 +10861,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10868,33 +10870,33 @@
         <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11006,10 +11008,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11123,10 +11125,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11152,16 +11154,16 @@
         <v>175</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -11186,13 +11188,13 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -11210,7 +11212,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -11231,7 +11233,7 @@
         <v>198</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -11242,10 +11244,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11268,19 +11270,19 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -11308,10 +11310,10 @@
         <v>157</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -11329,7 +11331,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -11347,10 +11349,10 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -11361,10 +11363,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11476,10 +11478,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11593,10 +11595,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11622,16 +11624,16 @@
         <v>153</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -11680,7 +11682,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11698,10 +11700,10 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -11712,10 +11714,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11827,10 +11829,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11944,10 +11946,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11973,16 +11975,16 @@
         <v>136</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11992,7 +11994,7 @@
         <v>78</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>78</v>
@@ -12031,7 +12033,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -12049,10 +12051,10 @@
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -12063,10 +12065,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12092,13 +12094,13 @@
         <v>103</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12148,7 +12150,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -12166,10 +12168,10 @@
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -12180,10 +12182,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12209,14 +12211,14 @@
         <v>175</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -12265,7 +12267,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -12283,10 +12285,10 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -12297,10 +12299,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12326,14 +12328,14 @@
         <v>103</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
@@ -12382,7 +12384,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12400,10 +12402,10 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -12414,10 +12416,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12440,19 +12442,19 @@
         <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -12501,7 +12503,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12519,10 +12521,10 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -12533,10 +12535,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12562,16 +12564,16 @@
         <v>103</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -12620,7 +12622,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12638,10 +12640,10 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>78</v>
@@ -12652,10 +12654,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12681,16 +12683,16 @@
         <v>136</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -12700,10 +12702,10 @@
         <v>78</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>78</v>
@@ -12739,7 +12741,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12757,13 +12759,13 @@
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>78</v>
@@ -12771,10 +12773,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12800,13 +12802,13 @@
         <v>103</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12820,7 +12822,7 @@
         <v>78</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>78</v>
@@ -12856,7 +12858,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12874,13 +12876,13 @@
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>78</v>
@@ -12888,10 +12890,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12914,13 +12916,13 @@
         <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12971,7 +12973,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12989,13 +12991,13 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>78</v>
@@ -13003,10 +13005,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13029,16 +13031,16 @@
         <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13088,7 +13090,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -13106,13 +13108,13 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>78</v>
@@ -13120,13 +13122,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>78</v>
@@ -13148,17 +13150,17 @@
         <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>78</v>
@@ -13207,7 +13209,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -13216,7 +13218,7 @@
         <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>101</v>
@@ -13225,24 +13227,24 @@
         <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13354,10 +13356,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13471,10 +13473,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13500,16 +13502,16 @@
         <v>175</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -13534,13 +13536,13 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -13558,7 +13560,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13579,7 +13581,7 @@
         <v>198</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>78</v>
@@ -13590,10 +13592,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13616,19 +13618,19 @@
         <v>90</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -13638,7 +13640,7 @@
         <v>78</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>78</v>
@@ -13656,10 +13658,10 @@
         <v>157</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -13677,7 +13679,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13695,10 +13697,10 @@
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -13709,10 +13711,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13738,16 +13740,16 @@
         <v>136</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -13757,10 +13759,10 @@
         <v>78</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>78</v>
@@ -13796,7 +13798,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13814,13 +13816,13 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>78</v>
@@ -13828,10 +13830,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13857,13 +13859,13 @@
         <v>103</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13877,7 +13879,7 @@
         <v>78</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>78</v>
@@ -13913,7 +13915,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13931,13 +13933,13 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>78</v>
@@ -13945,10 +13947,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13971,13 +13973,13 @@
         <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14028,7 +14030,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -14046,13 +14048,13 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>78</v>
@@ -14060,10 +14062,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14086,16 +14088,16 @@
         <v>90</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14145,7 +14147,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -14163,13 +14165,13 @@
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>78</v>
@@ -14177,13 +14179,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>78</v>
@@ -14205,17 +14207,17 @@
         <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -14264,7 +14266,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -14273,7 +14275,7 @@
         <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>101</v>
@@ -14282,24 +14284,24 @@
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14411,10 +14413,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14528,10 +14530,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14557,16 +14559,16 @@
         <v>175</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -14591,13 +14593,13 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -14615,7 +14617,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14636,7 +14638,7 @@
         <v>198</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -14647,10 +14649,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14673,19 +14675,19 @@
         <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -14695,7 +14697,7 @@
         <v>78</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>78</v>
@@ -14713,10 +14715,10 @@
         <v>157</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
@@ -14734,7 +14736,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14752,10 +14754,10 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -14766,10 +14768,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14795,16 +14797,16 @@
         <v>136</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -14814,10 +14816,10 @@
         <v>78</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>78</v>
@@ -14853,7 +14855,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14871,13 +14873,13 @@
         <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>78</v>
@@ -14885,10 +14887,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14914,13 +14916,13 @@
         <v>103</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14934,7 +14936,7 @@
         <v>78</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>78</v>
@@ -14970,7 +14972,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14988,13 +14990,13 @@
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>78</v>
@@ -15002,10 +15004,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15028,13 +15030,13 @@
         <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15085,7 +15087,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -15103,13 +15105,13 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>78</v>
@@ -15117,10 +15119,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15143,16 +15145,16 @@
         <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15202,7 +15204,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -15220,13 +15222,13 @@
         <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>78</v>
@@ -15234,10 +15236,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15260,70 +15262,70 @@
         <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q106" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="R106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF106" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q106" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="R106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -15341,24 +15343,24 @@
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15381,19 +15383,19 @@
         <v>90</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -15421,16 +15423,16 @@
         <v>165</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
@@ -15440,7 +15442,7 @@
         <v>116</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -15458,27 +15460,27 @@
         <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>78</v>
@@ -15500,19 +15502,19 @@
         <v>90</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -15537,11 +15539,11 @@
         <v>78</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>78</v>
@@ -15559,7 +15561,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15577,24 +15579,24 @@
         <v>78</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15706,10 +15708,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15821,13 +15823,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="B111" t="s" s="2">
-        <v>541</v>
-      </c>
       <c r="C111" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>78</v>
@@ -15849,13 +15851,13 @@
         <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15938,10 +15940,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16053,10 +16055,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16145,7 +16147,7 @@
         <v>80</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>118</v>
@@ -16168,10 +16170,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16197,13 +16199,13 @@
         <v>136</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16211,7 +16213,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>78</v>
@@ -16253,7 +16255,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>89</v>
@@ -16285,10 +16287,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16314,10 +16316,10 @@
         <v>175</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>556</v>
+        <v>232</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16329,7 +16331,7 @@
         <v>78</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>78</v>
@@ -16344,7 +16346,7 @@
         <v>78</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
@@ -16366,7 +16368,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16375,7 +16377,7 @@
         <v>89</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>101</v>
@@ -16427,16 +16429,16 @@
         <v>153</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -16485,7 +16487,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16503,10 +16505,10 @@
         <v>78</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>78</v>
@@ -16778,16 +16780,16 @@
         <v>136</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>78</v>
@@ -16836,7 +16838,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16854,10 +16856,10 @@
         <v>78</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>78</v>
@@ -16897,13 +16899,13 @@
         <v>103</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16953,7 +16955,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16971,10 +16973,10 @@
         <v>78</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>78</v>
@@ -17017,11 +17019,11 @@
         <v>570</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>78</v>
@@ -17070,7 +17072,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -17088,10 +17090,10 @@
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>78</v>
@@ -17131,14 +17133,14 @@
         <v>103</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -17187,7 +17189,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -17205,10 +17207,10 @@
         <v>78</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>78</v>
@@ -17245,19 +17247,19 @@
         <v>90</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -17306,7 +17308,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17324,10 +17326,10 @@
         <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>78</v>
@@ -17367,16 +17369,16 @@
         <v>103</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -17425,7 +17427,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17443,10 +17445,10 @@
         <v>78</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>78</v>
@@ -17460,7 +17462,7 @@
         <v>577</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>578</v>
@@ -17485,19 +17487,19 @@
         <v>90</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>579</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>78</v>
@@ -17522,7 +17524,7 @@
         <v>78</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
@@ -17544,7 +17546,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17562,16 +17564,16 @@
         <v>78</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="126" hidden="true">
@@ -17579,7 +17581,7 @@
         <v>581</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17694,7 +17696,7 @@
         <v>582</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17837,16 +17839,16 @@
         <v>153</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>78</v>
@@ -17895,7 +17897,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17913,10 +17915,10 @@
         <v>78</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>78</v>
@@ -18188,16 +18190,16 @@
         <v>136</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>78</v>
@@ -18246,7 +18248,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -18264,10 +18266,10 @@
         <v>78</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>78</v>
@@ -18307,13 +18309,13 @@
         <v>103</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18363,7 +18365,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18381,10 +18383,10 @@
         <v>78</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>78</v>
@@ -18427,11 +18429,11 @@
         <v>570</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>78</v>
@@ -18480,7 +18482,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18498,10 +18500,10 @@
         <v>78</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>78</v>
@@ -18541,14 +18543,14 @@
         <v>103</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -18597,7 +18599,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18615,10 +18617,10 @@
         <v>78</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>78</v>
@@ -18655,19 +18657,19 @@
         <v>90</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>78</v>
@@ -18716,7 +18718,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18734,10 +18736,10 @@
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>78</v>
@@ -18777,16 +18779,16 @@
         <v>103</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>78</v>
@@ -18835,7 +18837,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18853,10 +18855,10 @@
         <v>78</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>78</v>
@@ -18870,7 +18872,7 @@
         <v>592</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C137" t="s" s="2">
         <v>593</v>
@@ -18895,19 +18897,19 @@
         <v>90</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L137" t="s" s="2">
         <v>594</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>78</v>
@@ -18932,7 +18934,7 @@
         <v>78</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
@@ -18954,7 +18956,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18972,16 +18974,16 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="138" hidden="true">
@@ -18989,7 +18991,7 @@
         <v>596</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19104,7 +19106,7 @@
         <v>597</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19247,16 +19249,16 @@
         <v>153</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>78</v>
@@ -19305,7 +19307,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19323,10 +19325,10 @@
         <v>78</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>78</v>
@@ -19598,16 +19600,16 @@
         <v>136</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>78</v>
@@ -19656,7 +19658,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19674,10 +19676,10 @@
         <v>78</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>78</v>
@@ -19717,13 +19719,13 @@
         <v>103</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19773,7 +19775,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -19791,10 +19793,10 @@
         <v>78</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>78</v>
@@ -19837,11 +19839,11 @@
         <v>570</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -19890,7 +19892,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -19908,10 +19910,10 @@
         <v>78</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>78</v>
@@ -19951,14 +19953,14 @@
         <v>103</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -20007,7 +20009,7 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -20025,10 +20027,10 @@
         <v>78</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>78</v>
@@ -20065,19 +20067,19 @@
         <v>90</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>78</v>
@@ -20126,7 +20128,7 @@
         <v>78</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -20144,10 +20146,10 @@
         <v>78</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>78</v>
@@ -20187,16 +20189,16 @@
         <v>103</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>78</v>
@@ -20245,7 +20247,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20263,10 +20265,10 @@
         <v>78</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>78</v>
@@ -20280,7 +20282,7 @@
         <v>607</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C149" t="s" s="2">
         <v>608</v>
@@ -20305,19 +20307,19 @@
         <v>90</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L149" t="s" s="2">
         <v>609</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>78</v>
@@ -20342,7 +20344,7 @@
         <v>78</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
@@ -20364,7 +20366,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20382,16 +20384,16 @@
         <v>611</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="150" hidden="true">
@@ -20399,7 +20401,7 @@
         <v>612</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20514,7 +20516,7 @@
         <v>613</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20603,7 +20605,7 @@
         <v>80</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>118</v>
@@ -20629,10 +20631,10 @@
         <v>614</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>78</v>
@@ -20654,13 +20656,13 @@
         <v>78</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -20720,7 +20722,7 @@
         <v>80</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>118</v>
@@ -20746,7 +20748,7 @@
         <v>615</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20861,7 +20863,7 @@
         <v>616</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20950,7 +20952,7 @@
         <v>80</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>118</v>
@@ -20976,7 +20978,7 @@
         <v>617</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21002,13 +21004,13 @@
         <v>136</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21016,7 +21018,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>78</v>
@@ -21058,7 +21060,7 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>89</v>
@@ -21093,7 +21095,7 @@
         <v>618</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21119,10 +21121,10 @@
         <v>175</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>556</v>
+        <v>232</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21149,7 +21151,7 @@
         <v>78</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
@@ -21171,7 +21173,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21180,7 +21182,7 @@
         <v>89</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>101</v>
@@ -21232,16 +21234,16 @@
         <v>153</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>78</v>
@@ -21290,7 +21292,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21299,7 +21301,7 @@
         <v>80</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>101</v>
@@ -21308,10 +21310,10 @@
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>78</v>
@@ -21351,16 +21353,16 @@
         <v>103</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>78</v>
@@ -21409,7 +21411,7 @@
         <v>78</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21418,7 +21420,7 @@
         <v>89</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>101</v>
@@ -21427,10 +21429,10 @@
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>78</v>
@@ -21444,7 +21446,7 @@
         <v>621</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C159" t="s" s="2">
         <v>622</v>
@@ -21469,19 +21471,19 @@
         <v>90</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L159" t="s" s="2">
         <v>623</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
@@ -21506,7 +21508,7 @@
         <v>78</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
@@ -21528,7 +21530,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21546,16 +21548,16 @@
         <v>625</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="160" hidden="true">
@@ -21563,7 +21565,7 @@
         <v>626</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21678,7 +21680,7 @@
         <v>627</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21767,7 +21769,7 @@
         <v>80</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>118</v>
@@ -21793,10 +21795,10 @@
         <v>628</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>78</v>
@@ -21818,13 +21820,13 @@
         <v>78</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -21884,7 +21886,7 @@
         <v>80</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>118</v>
@@ -21910,7 +21912,7 @@
         <v>629</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22025,7 +22027,7 @@
         <v>630</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22114,7 +22116,7 @@
         <v>80</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>118</v>
@@ -22140,7 +22142,7 @@
         <v>631</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22166,13 +22168,13 @@
         <v>136</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22180,7 +22182,7 @@
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>78</v>
@@ -22222,7 +22224,7 @@
         <v>78</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>89</v>
@@ -22257,7 +22259,7 @@
         <v>632</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22283,10 +22285,10 @@
         <v>175</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>556</v>
+        <v>232</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22313,7 +22315,7 @@
         <v>78</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
@@ -22335,7 +22337,7 @@
         <v>78</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22344,7 +22346,7 @@
         <v>89</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>101</v>
@@ -22396,16 +22398,16 @@
         <v>153</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>78</v>
@@ -22454,7 +22456,7 @@
         <v>78</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22463,7 +22465,7 @@
         <v>80</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ167" t="s" s="2">
         <v>101</v>
@@ -22472,10 +22474,10 @@
         <v>78</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>78</v>
@@ -22515,16 +22517,16 @@
         <v>103</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>78</v>
@@ -22573,7 +22575,7 @@
         <v>78</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -22582,7 +22584,7 @@
         <v>89</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>101</v>
@@ -22591,10 +22593,10 @@
         <v>78</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>78</v>
@@ -22608,7 +22610,7 @@
         <v>635</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C169" t="s" s="2">
         <v>636</v>
@@ -22633,19 +22635,19 @@
         <v>90</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L169" t="s" s="2">
         <v>637</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>78</v>
@@ -22670,7 +22672,7 @@
         <v>78</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
@@ -22692,7 +22694,7 @@
         <v>78</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -22710,16 +22712,16 @@
         <v>78</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="170" hidden="true">
@@ -22727,7 +22729,7 @@
         <v>639</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22842,7 +22844,7 @@
         <v>640</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22931,7 +22933,7 @@
         <v>80</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>118</v>
@@ -22957,10 +22959,10 @@
         <v>641</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>78</v>
@@ -22982,13 +22984,13 @@
         <v>78</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23048,7 +23050,7 @@
         <v>80</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>118</v>
@@ -23074,7 +23076,7 @@
         <v>642</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23189,7 +23191,7 @@
         <v>643</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23278,7 +23280,7 @@
         <v>80</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>118</v>
@@ -23304,7 +23306,7 @@
         <v>644</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23330,13 +23332,13 @@
         <v>136</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23344,7 +23346,7 @@
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>78</v>
@@ -23386,7 +23388,7 @@
         <v>78</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>89</v>
@@ -23421,7 +23423,7 @@
         <v>645</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23447,10 +23449,10 @@
         <v>175</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>556</v>
+        <v>232</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23477,7 +23479,7 @@
         <v>78</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
@@ -23499,7 +23501,7 @@
         <v>78</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
@@ -23508,7 +23510,7 @@
         <v>89</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>101</v>
@@ -23560,16 +23562,16 @@
         <v>153</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>78</v>
@@ -23618,7 +23620,7 @@
         <v>78</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23627,7 +23629,7 @@
         <v>80</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>101</v>
@@ -23636,10 +23638,10 @@
         <v>78</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>78</v>
@@ -23679,16 +23681,16 @@
         <v>103</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>78</v>
@@ -23737,7 +23739,7 @@
         <v>78</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23746,7 +23748,7 @@
         <v>89</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>101</v>
@@ -23755,10 +23757,10 @@
         <v>78</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>78</v>
@@ -23772,7 +23774,7 @@
         <v>648</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C179" t="s" s="2">
         <v>649</v>
@@ -23797,19 +23799,19 @@
         <v>90</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L179" t="s" s="2">
         <v>650</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>78</v>
@@ -23837,10 +23839,10 @@
         <v>165</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>78</v>
@@ -23858,7 +23860,7 @@
         <v>78</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -23876,16 +23878,16 @@
         <v>78</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="180" hidden="true">
@@ -23893,7 +23895,7 @@
         <v>651</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24008,7 +24010,7 @@
         <v>652</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24097,7 +24099,7 @@
         <v>80</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>118</v>
@@ -24123,10 +24125,10 @@
         <v>653</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>78</v>
@@ -24148,13 +24150,13 @@
         <v>78</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -24214,7 +24216,7 @@
         <v>80</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>118</v>
@@ -24240,7 +24242,7 @@
         <v>654</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24355,7 +24357,7 @@
         <v>655</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24444,7 +24446,7 @@
         <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>118</v>
@@ -24470,7 +24472,7 @@
         <v>656</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24496,13 +24498,13 @@
         <v>136</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -24510,7 +24512,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>78</v>
@@ -24552,7 +24554,7 @@
         <v>78</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>89</v>
@@ -24587,7 +24589,7 @@
         <v>657</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24613,10 +24615,10 @@
         <v>175</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>556</v>
+        <v>232</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -24643,7 +24645,7 @@
         <v>78</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
@@ -24665,7 +24667,7 @@
         <v>78</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -24674,7 +24676,7 @@
         <v>89</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>101</v>
@@ -24726,16 +24728,16 @@
         <v>153</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>78</v>
@@ -24784,7 +24786,7 @@
         <v>78</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -24793,7 +24795,7 @@
         <v>80</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>101</v>
@@ -24802,10 +24804,10 @@
         <v>78</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>78</v>
@@ -24845,16 +24847,16 @@
         <v>103</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>78</v>
@@ -24903,7 +24905,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -24912,7 +24914,7 @@
         <v>89</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>101</v>
@@ -24921,10 +24923,10 @@
         <v>78</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>78</v>
@@ -25031,7 +25033,7 @@
         <v>89</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>101</v>
@@ -25698,7 +25700,7 @@
         <v>78</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y195" t="s" s="2">
         <v>697</v>
@@ -25865,7 +25867,7 @@
         <v>711</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>78</v>
@@ -25936,7 +25938,7 @@
         <v>78</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y197" t="s" s="2">
         <v>717</v>
@@ -26135,7 +26137,7 @@
         <v>90</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L199" t="s" s="2">
         <v>730</v>
@@ -26216,7 +26218,7 @@
         <v>733</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>78</v>
@@ -26567,7 +26569,7 @@
         <v>78</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AM202" t="s" s="2">
         <v>755</v>
@@ -26995,7 +26997,7 @@
       </c>
       <c r="Y206" s="2"/>
       <c r="Z206" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>78</v>
@@ -27071,7 +27073,7 @@
         <v>90</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L207" t="s" s="2">
         <v>770</v>
@@ -27668,7 +27670,7 @@
         <v>113</v>
       </c>
       <c r="O212" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>78</v>
@@ -27775,7 +27777,7 @@
         <v>78</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L213" t="s" s="2">
         <v>795</v>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8078" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8077" uniqueCount="821">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T12:18:24+00:00</t>
+    <t>2024-04-10T12:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -689,9 +689,6 @@
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
     <t>The date range that this organization should be considered available.</t>
   </si>
   <si>
@@ -741,7 +738,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -781,8 +778,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t>ele-1
-per-1</t>
+    <t xml:space="preserve">per-1
+</t>
   </si>
   <si>
     <t>dateCreation</t>
@@ -1746,6 +1743,9 @@
   </si>
   <si>
     <t>Organization.type.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-organization-types</t>
@@ -5413,10 +5413,10 @@
         <v>214</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5488,7 +5488,7 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5614,14 +5614,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5643,14 +5643,12 @@
         <v>110</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>111</v>
+        <v>200</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -5708,7 +5706,7 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>118</v>
@@ -5720,7 +5718,7 @@
         <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -5731,10 +5729,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5760,13 +5758,13 @@
         <v>136</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5774,49 +5772,49 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="S25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>89</v>
@@ -5848,10 +5846,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5874,13 +5872,13 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5931,7 +5929,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5940,7 +5938,7 @@
         <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>101</v>
@@ -5963,10 +5961,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6078,10 +6076,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6172,7 +6170,7 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>118</v>
@@ -6184,7 +6182,7 @@
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -6195,10 +6193,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6221,16 +6219,16 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6280,28 +6278,28 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI29" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -6312,10 +6310,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6338,69 +6336,69 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q30" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="R30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="R30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>255</v>
-      </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
@@ -6408,19 +6406,19 @@
         <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -6431,13 +6429,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>78</v>
@@ -6459,13 +6457,13 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6548,13 +6546,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>78</v>
@@ -6576,13 +6574,13 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6648,7 +6646,7 @@
         <v>118</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>78</v>
@@ -6665,13 +6663,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>78</v>
@@ -6693,13 +6691,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6782,13 +6780,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>78</v>
@@ -6810,13 +6808,13 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6882,7 +6880,7 @@
         <v>118</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>78</v>
@@ -6899,13 +6897,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>78</v>
@@ -6927,13 +6925,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7016,13 +7014,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>78</v>
@@ -7044,13 +7042,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7133,10 +7131,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7162,16 +7160,16 @@
         <v>110</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -7220,7 +7218,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -7252,10 +7250,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7278,17 +7276,17 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -7325,10 +7323,10 @@
         <v>78</v>
       </c>
       <c r="AB38" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AC38" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>78</v>
@@ -7337,7 +7335,7 @@
         <v>116</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -7346,7 +7344,7 @@
         <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>101</v>
@@ -7355,27 +7353,27 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>78</v>
@@ -7397,17 +7395,17 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -7456,7 +7454,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7465,33 +7463,33 @@
         <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7603,10 +7601,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7720,10 +7718,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7749,16 +7747,16 @@
         <v>175</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7768,46 +7766,46 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X42" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="T42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X42" t="s" s="2">
+      <c r="Y42" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="Y42" t="s" s="2">
+      <c r="Z42" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AA42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7828,7 +7826,7 @@
         <v>198</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -7839,10 +7837,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7865,19 +7863,19 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -7887,7 +7885,7 @@
         <v>78</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>78</v>
@@ -7905,28 +7903,28 @@
         <v>157</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="Z43" t="s" s="2">
+      <c r="AA43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7944,10 +7942,10 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -7958,10 +7956,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7987,16 +7985,16 @@
         <v>136</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -8006,46 +8004,46 @@
         <v>78</v>
       </c>
       <c r="S44" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="T44" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="T44" t="s" s="2">
+      <c r="U44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -8063,13 +8061,13 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -8077,10 +8075,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8106,13 +8104,13 @@
         <v>103</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8126,43 +8124,43 @@
         <v>78</v>
       </c>
       <c r="T45" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -8180,13 +8178,13 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AN45" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>78</v>
@@ -8194,10 +8192,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8220,13 +8218,13 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8277,7 +8275,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -8295,13 +8293,13 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -8309,10 +8307,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8335,16 +8333,16 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8394,7 +8392,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8412,13 +8410,13 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
@@ -8426,13 +8424,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C48" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>78</v>
@@ -8454,17 +8452,17 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -8513,7 +8511,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8522,33 +8520,33 @@
         <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8660,10 +8658,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8777,10 +8775,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8806,16 +8804,16 @@
         <v>175</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -8840,31 +8838,31 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Y51" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="Y51" t="s" s="2">
+      <c r="Z51" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="Z51" t="s" s="2">
+      <c r="AA51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8885,7 +8883,7 @@
         <v>198</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -8896,10 +8894,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8922,19 +8920,19 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -8962,28 +8960,28 @@
         <v>157</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="Z52" t="s" s="2">
+      <c r="AA52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -9001,10 +8999,10 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -9015,10 +9013,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9130,10 +9128,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9247,10 +9245,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9276,16 +9274,16 @@
         <v>153</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -9334,7 +9332,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9352,10 +9350,10 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -9366,10 +9364,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9481,10 +9479,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9598,10 +9596,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9627,16 +9625,16 @@
         <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -9646,46 +9644,46 @@
         <v>78</v>
       </c>
       <c r="S58" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9703,10 +9701,10 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -9717,10 +9715,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9746,13 +9744,13 @@
         <v>103</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9802,7 +9800,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9820,10 +9818,10 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -9834,10 +9832,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9863,14 +9861,14 @@
         <v>175</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9919,7 +9917,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9937,10 +9935,10 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -9951,10 +9949,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9980,14 +9978,14 @@
         <v>103</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -10036,7 +10034,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -10054,10 +10052,10 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -10068,10 +10066,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10094,19 +10092,19 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
@@ -10155,7 +10153,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -10173,10 +10171,10 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -10187,10 +10185,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10216,16 +10214,16 @@
         <v>103</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -10274,7 +10272,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -10292,10 +10290,10 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -10306,10 +10304,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10335,16 +10333,16 @@
         <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -10354,46 +10352,46 @@
         <v>78</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T64" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10411,13 +10409,13 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -10425,10 +10423,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10454,13 +10452,13 @@
         <v>103</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M65" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10474,43 +10472,43 @@
         <v>78</v>
       </c>
       <c r="T65" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10528,13 +10526,13 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AN65" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -10542,10 +10540,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10568,13 +10566,13 @@
         <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10625,7 +10623,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10643,13 +10641,13 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -10657,10 +10655,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10683,16 +10681,16 @@
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10742,7 +10740,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10760,13 +10758,13 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -10774,13 +10772,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C68" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>78</v>
@@ -10802,17 +10800,17 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10861,7 +10859,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10870,33 +10868,33 @@
         <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AN68" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11008,10 +11006,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11125,10 +11123,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11154,16 +11152,16 @@
         <v>175</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -11188,31 +11186,31 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Y71" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="Y71" t="s" s="2">
+      <c r="Z71" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="Z71" t="s" s="2">
+      <c r="AA71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -11233,7 +11231,7 @@
         <v>198</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -11244,10 +11242,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11270,19 +11268,19 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -11310,28 +11308,28 @@
         <v>157</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="Z72" t="s" s="2">
+      <c r="AA72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -11349,10 +11347,10 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -11363,10 +11361,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11478,10 +11476,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11595,10 +11593,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11624,16 +11622,16 @@
         <v>153</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -11682,7 +11680,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11700,10 +11698,10 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -11714,10 +11712,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11829,10 +11827,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11946,10 +11944,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11975,16 +11973,16 @@
         <v>136</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11994,46 +11992,46 @@
         <v>78</v>
       </c>
       <c r="S78" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -12051,10 +12049,10 @@
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -12065,10 +12063,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12094,13 +12092,13 @@
         <v>103</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12150,7 +12148,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -12168,10 +12166,10 @@
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -12182,10 +12180,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12211,14 +12209,14 @@
         <v>175</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -12267,7 +12265,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -12285,10 +12283,10 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -12299,10 +12297,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12328,14 +12326,14 @@
         <v>103</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
@@ -12384,7 +12382,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12402,10 +12400,10 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -12416,10 +12414,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12442,19 +12440,19 @@
         <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -12503,7 +12501,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12521,10 +12519,10 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM82" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -12535,10 +12533,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12564,16 +12562,16 @@
         <v>103</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -12622,7 +12620,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12640,10 +12638,10 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>78</v>
@@ -12654,10 +12652,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12683,16 +12681,16 @@
         <v>136</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -12702,46 +12700,46 @@
         <v>78</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="T84" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12759,13 +12757,13 @@
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>78</v>
@@ -12773,10 +12771,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12802,13 +12800,13 @@
         <v>103</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M85" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12822,43 +12820,43 @@
         <v>78</v>
       </c>
       <c r="T85" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12876,13 +12874,13 @@
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AM85" t="s" s="2">
+      <c r="AN85" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>78</v>
@@ -12890,10 +12888,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12916,13 +12914,13 @@
         <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12973,7 +12971,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12991,13 +12989,13 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AM86" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AM86" t="s" s="2">
+      <c r="AN86" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>78</v>
@@ -13005,10 +13003,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13031,16 +13029,16 @@
         <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13090,7 +13088,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -13108,13 +13106,13 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AM87" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AM87" t="s" s="2">
+      <c r="AN87" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>78</v>
@@ -13122,13 +13120,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C88" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>78</v>
@@ -13150,17 +13148,17 @@
         <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>78</v>
@@ -13209,7 +13207,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -13218,7 +13216,7 @@
         <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>101</v>
@@ -13227,24 +13225,24 @@
         <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM88" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AM88" t="s" s="2">
+      <c r="AN88" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AN88" t="s" s="2">
+      <c r="AO88" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13356,10 +13354,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13473,10 +13471,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13502,16 +13500,16 @@
         <v>175</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -13536,31 +13534,31 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Y91" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="Y91" t="s" s="2">
+      <c r="Z91" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="Z91" t="s" s="2">
+      <c r="AA91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13581,7 +13579,7 @@
         <v>198</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>78</v>
@@ -13592,10 +13590,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13618,19 +13616,19 @@
         <v>90</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -13640,7 +13638,7 @@
         <v>78</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>78</v>
@@ -13658,28 +13656,28 @@
         <v>157</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="Z92" t="s" s="2">
+      <c r="AA92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13697,10 +13695,10 @@
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -13711,10 +13709,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13740,16 +13738,16 @@
         <v>136</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -13759,46 +13757,46 @@
         <v>78</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="T93" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13816,13 +13814,13 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>78</v>
@@ -13830,10 +13828,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13859,13 +13857,13 @@
         <v>103</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M94" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13879,43 +13877,43 @@
         <v>78</v>
       </c>
       <c r="T94" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13933,13 +13931,13 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AM94" t="s" s="2">
+      <c r="AN94" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>78</v>
@@ -13947,10 +13945,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13973,13 +13971,13 @@
         <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14030,7 +14028,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -14048,13 +14046,13 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AM95" t="s" s="2">
+      <c r="AN95" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>78</v>
@@ -14062,10 +14060,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14088,16 +14086,16 @@
         <v>90</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14147,7 +14145,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -14165,13 +14163,13 @@
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AM96" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AM96" t="s" s="2">
+      <c r="AN96" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>78</v>
@@ -14179,13 +14177,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C97" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>78</v>
@@ -14207,17 +14205,17 @@
         <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -14266,7 +14264,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -14275,7 +14273,7 @@
         <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>101</v>
@@ -14284,24 +14282,24 @@
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM97" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AM97" t="s" s="2">
+      <c r="AN97" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AN97" t="s" s="2">
+      <c r="AO97" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14413,10 +14411,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14530,10 +14528,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14559,16 +14557,16 @@
         <v>175</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -14593,31 +14591,31 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Y100" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="Y100" t="s" s="2">
+      <c r="Z100" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="Z100" t="s" s="2">
+      <c r="AA100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14638,7 +14636,7 @@
         <v>198</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -14649,10 +14647,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14675,19 +14673,19 @@
         <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -14697,7 +14695,7 @@
         <v>78</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>78</v>
@@ -14715,28 +14713,28 @@
         <v>157</v>
       </c>
       <c r="Y101" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="Z101" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="Z101" t="s" s="2">
+      <c r="AA101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14754,10 +14752,10 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -14768,10 +14766,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14797,16 +14795,16 @@
         <v>136</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -14816,46 +14814,46 @@
         <v>78</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="T102" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14873,13 +14871,13 @@
         <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM102" t="s" s="2">
+      <c r="AN102" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>78</v>
@@ -14887,10 +14885,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14916,13 +14914,13 @@
         <v>103</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M103" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14936,43 +14934,43 @@
         <v>78</v>
       </c>
       <c r="T103" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14990,13 +14988,13 @@
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AM103" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AM103" t="s" s="2">
+      <c r="AN103" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>78</v>
@@ -15004,10 +15002,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15030,13 +15028,13 @@
         <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15087,7 +15085,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -15105,13 +15103,13 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AM104" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AM104" t="s" s="2">
+      <c r="AN104" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>78</v>
@@ -15119,10 +15117,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15145,16 +15143,16 @@
         <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15204,7 +15202,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -15222,13 +15220,13 @@
         <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AM105" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AM105" t="s" s="2">
+      <c r="AN105" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>78</v>
@@ -15236,10 +15234,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15262,26 +15260,26 @@
         <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="N106" t="s" s="2">
+      <c r="O106" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="O106" t="s" s="2">
+      <c r="P106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q106" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="P106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q106" t="s" s="2">
-        <v>519</v>
-      </c>
       <c r="R106" t="s" s="2">
         <v>78</v>
       </c>
@@ -15325,7 +15323,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -15343,24 +15341,24 @@
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AM106" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="AM106" t="s" s="2">
+      <c r="AN106" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AN106" t="s" s="2">
+      <c r="AO106" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>523</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15383,19 +15381,19 @@
         <v>90</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -15423,16 +15421,16 @@
         <v>165</v>
       </c>
       <c r="Y107" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="Z107" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="Z107" t="s" s="2">
+      <c r="AA107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB107" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
@@ -15442,7 +15440,7 @@
         <v>116</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -15460,27 +15458,27 @@
         <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AM107" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C108" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>78</v>
@@ -15502,19 +15500,19 @@
         <v>90</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="M108" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -15539,11 +15537,11 @@
         <v>78</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>78</v>
@@ -15561,7 +15559,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15579,24 +15577,24 @@
         <v>78</v>
       </c>
       <c r="AL108" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AM108" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15708,10 +15706,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15823,13 +15821,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C111" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>78</v>
@@ -15851,13 +15849,13 @@
         <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15940,10 +15938,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16055,10 +16053,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16147,7 +16145,7 @@
         <v>80</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>118</v>
@@ -16170,10 +16168,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16199,13 +16197,13 @@
         <v>136</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16213,7 +16211,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>78</v>
@@ -16255,7 +16253,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>89</v>
@@ -16287,10 +16285,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16316,10 +16314,10 @@
         <v>175</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>232</v>
+        <v>556</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16331,7 +16329,7 @@
         <v>78</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>78</v>
@@ -16346,7 +16344,7 @@
         <v>78</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
@@ -16368,7 +16366,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16377,7 +16375,7 @@
         <v>89</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>101</v>
@@ -16429,16 +16427,16 @@
         <v>153</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N116" t="s" s="2">
+      <c r="O116" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -16487,7 +16485,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16505,10 +16503,10 @@
         <v>78</v>
       </c>
       <c r="AL116" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM116" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>78</v>
@@ -16780,16 +16778,16 @@
         <v>136</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N119" t="s" s="2">
+      <c r="O119" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>78</v>
@@ -16838,7 +16836,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16856,10 +16854,10 @@
         <v>78</v>
       </c>
       <c r="AL119" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AM119" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>78</v>
@@ -16899,13 +16897,13 @@
         <v>103</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16955,7 +16953,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16973,10 +16971,10 @@
         <v>78</v>
       </c>
       <c r="AL120" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AM120" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>78</v>
@@ -17019,11 +17017,11 @@
         <v>570</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>78</v>
@@ -17072,7 +17070,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -17090,10 +17088,10 @@
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM121" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>78</v>
@@ -17133,14 +17131,14 @@
         <v>103</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -17189,7 +17187,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -17207,10 +17205,10 @@
         <v>78</v>
       </c>
       <c r="AL122" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AM122" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>78</v>
@@ -17247,19 +17245,19 @@
         <v>90</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L123" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="M123" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -17308,7 +17306,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17326,10 +17324,10 @@
         <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM123" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>78</v>
@@ -17369,16 +17367,16 @@
         <v>103</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N124" t="s" s="2">
+      <c r="O124" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -17427,7 +17425,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17445,10 +17443,10 @@
         <v>78</v>
       </c>
       <c r="AL124" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AM124" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>78</v>
@@ -17462,7 +17460,7 @@
         <v>577</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>578</v>
@@ -17487,19 +17485,19 @@
         <v>90</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>579</v>
       </c>
       <c r="M125" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N125" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="N125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>78</v>
@@ -17524,7 +17522,7 @@
         <v>78</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
@@ -17546,7 +17544,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17564,16 +17562,16 @@
         <v>78</v>
       </c>
       <c r="AL125" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AM125" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="126" hidden="true">
@@ -17581,7 +17579,7 @@
         <v>581</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17696,7 +17694,7 @@
         <v>582</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17839,16 +17837,16 @@
         <v>153</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>78</v>
@@ -17897,7 +17895,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17915,10 +17913,10 @@
         <v>78</v>
       </c>
       <c r="AL128" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM128" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>78</v>
@@ -18190,16 +18188,16 @@
         <v>136</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>78</v>
@@ -18248,7 +18246,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -18266,10 +18264,10 @@
         <v>78</v>
       </c>
       <c r="AL131" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AM131" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>78</v>
@@ -18309,13 +18307,13 @@
         <v>103</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18365,7 +18363,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18383,10 +18381,10 @@
         <v>78</v>
       </c>
       <c r="AL132" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AM132" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>78</v>
@@ -18429,11 +18427,11 @@
         <v>570</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>78</v>
@@ -18482,7 +18480,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18500,10 +18498,10 @@
         <v>78</v>
       </c>
       <c r="AL133" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM133" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>78</v>
@@ -18543,14 +18541,14 @@
         <v>103</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -18599,7 +18597,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18617,10 +18615,10 @@
         <v>78</v>
       </c>
       <c r="AL134" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AM134" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>78</v>
@@ -18657,19 +18655,19 @@
         <v>90</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L135" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L135" t="s" s="2">
+      <c r="M135" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>78</v>
@@ -18718,7 +18716,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18736,10 +18734,10 @@
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM135" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>78</v>
@@ -18779,16 +18777,16 @@
         <v>103</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>78</v>
@@ -18837,7 +18835,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18855,10 +18853,10 @@
         <v>78</v>
       </c>
       <c r="AL136" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AM136" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>78</v>
@@ -18872,7 +18870,7 @@
         <v>592</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C137" t="s" s="2">
         <v>593</v>
@@ -18897,19 +18895,19 @@
         <v>90</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L137" t="s" s="2">
         <v>594</v>
       </c>
       <c r="M137" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N137" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="N137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>78</v>
@@ -18934,7 +18932,7 @@
         <v>78</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
@@ -18956,7 +18954,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18974,16 +18972,16 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AM137" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="138" hidden="true">
@@ -18991,7 +18989,7 @@
         <v>596</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19106,7 +19104,7 @@
         <v>597</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19249,16 +19247,16 @@
         <v>153</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N140" t="s" s="2">
+      <c r="O140" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>78</v>
@@ -19307,7 +19305,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19325,10 +19323,10 @@
         <v>78</v>
       </c>
       <c r="AL140" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM140" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AM140" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>78</v>
@@ -19600,16 +19598,16 @@
         <v>136</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N143" t="s" s="2">
+      <c r="O143" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>78</v>
@@ -19658,7 +19656,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19676,10 +19674,10 @@
         <v>78</v>
       </c>
       <c r="AL143" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AM143" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AM143" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>78</v>
@@ -19719,13 +19717,13 @@
         <v>103</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="N144" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19775,7 +19773,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -19793,10 +19791,10 @@
         <v>78</v>
       </c>
       <c r="AL144" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AM144" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM144" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>78</v>
@@ -19839,11 +19837,11 @@
         <v>570</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -19892,7 +19890,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -19910,10 +19908,10 @@
         <v>78</v>
       </c>
       <c r="AL145" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM145" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AM145" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>78</v>
@@ -19953,14 +19951,14 @@
         <v>103</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -20009,7 +20007,7 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -20027,10 +20025,10 @@
         <v>78</v>
       </c>
       <c r="AL146" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AM146" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AM146" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>78</v>
@@ -20067,19 +20065,19 @@
         <v>90</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N147" t="s" s="2">
+      <c r="O147" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>78</v>
@@ -20128,7 +20126,7 @@
         <v>78</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -20146,10 +20144,10 @@
         <v>78</v>
       </c>
       <c r="AL147" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM147" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AM147" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>78</v>
@@ -20189,16 +20187,16 @@
         <v>103</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N148" t="s" s="2">
+      <c r="O148" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>78</v>
@@ -20247,7 +20245,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20265,10 +20263,10 @@
         <v>78</v>
       </c>
       <c r="AL148" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AM148" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AM148" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>78</v>
@@ -20282,7 +20280,7 @@
         <v>607</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C149" t="s" s="2">
         <v>608</v>
@@ -20307,19 +20305,19 @@
         <v>90</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L149" t="s" s="2">
         <v>609</v>
       </c>
       <c r="M149" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="N149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>78</v>
@@ -20344,7 +20342,7 @@
         <v>78</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
@@ -20366,7 +20364,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20384,16 +20382,16 @@
         <v>611</v>
       </c>
       <c r="AL149" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AM149" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AM149" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="150" hidden="true">
@@ -20401,7 +20399,7 @@
         <v>612</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20516,7 +20514,7 @@
         <v>613</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20605,7 +20603,7 @@
         <v>80</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>118</v>
@@ -20631,10 +20629,10 @@
         <v>614</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>78</v>
@@ -20656,13 +20654,13 @@
         <v>78</v>
       </c>
       <c r="K152" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L152" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="L152" t="s" s="2">
+      <c r="M152" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -20722,7 +20720,7 @@
         <v>80</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>118</v>
@@ -20748,7 +20746,7 @@
         <v>615</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20863,7 +20861,7 @@
         <v>616</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20952,7 +20950,7 @@
         <v>80</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>118</v>
@@ -20978,7 +20976,7 @@
         <v>617</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21004,13 +21002,13 @@
         <v>136</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M155" t="s" s="2">
+      <c r="N155" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21018,7 +21016,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>78</v>
@@ -21060,7 +21058,7 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>89</v>
@@ -21095,7 +21093,7 @@
         <v>618</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21121,10 +21119,10 @@
         <v>175</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>232</v>
+        <v>556</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21151,7 +21149,7 @@
         <v>78</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
@@ -21173,7 +21171,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21182,7 +21180,7 @@
         <v>89</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>101</v>
@@ -21234,16 +21232,16 @@
         <v>153</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N157" t="s" s="2">
+      <c r="O157" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>78</v>
@@ -21292,7 +21290,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21301,7 +21299,7 @@
         <v>80</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>101</v>
@@ -21310,10 +21308,10 @@
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM157" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AM157" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>78</v>
@@ -21353,16 +21351,16 @@
         <v>103</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M158" t="s" s="2">
+      <c r="N158" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N158" t="s" s="2">
+      <c r="O158" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>78</v>
@@ -21411,7 +21409,7 @@
         <v>78</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21420,7 +21418,7 @@
         <v>89</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>101</v>
@@ -21429,10 +21427,10 @@
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AM158" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AM158" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>78</v>
@@ -21446,7 +21444,7 @@
         <v>621</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C159" t="s" s="2">
         <v>622</v>
@@ -21471,19 +21469,19 @@
         <v>90</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L159" t="s" s="2">
         <v>623</v>
       </c>
       <c r="M159" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N159" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="N159" t="s" s="2">
+      <c r="O159" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
@@ -21508,7 +21506,7 @@
         <v>78</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
@@ -21530,7 +21528,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21548,16 +21546,16 @@
         <v>625</v>
       </c>
       <c r="AL159" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AM159" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AM159" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="160" hidden="true">
@@ -21565,7 +21563,7 @@
         <v>626</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21680,7 +21678,7 @@
         <v>627</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21769,7 +21767,7 @@
         <v>80</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>118</v>
@@ -21795,10 +21793,10 @@
         <v>628</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>78</v>
@@ -21820,13 +21818,13 @@
         <v>78</v>
       </c>
       <c r="K162" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L162" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="L162" t="s" s="2">
+      <c r="M162" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -21886,7 +21884,7 @@
         <v>80</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>118</v>
@@ -21912,7 +21910,7 @@
         <v>629</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22027,7 +22025,7 @@
         <v>630</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22116,7 +22114,7 @@
         <v>80</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>118</v>
@@ -22142,7 +22140,7 @@
         <v>631</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22168,13 +22166,13 @@
         <v>136</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M165" t="s" s="2">
+      <c r="N165" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22182,7 +22180,7 @@
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>78</v>
@@ -22224,7 +22222,7 @@
         <v>78</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>89</v>
@@ -22259,7 +22257,7 @@
         <v>632</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22285,10 +22283,10 @@
         <v>175</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>232</v>
+        <v>556</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22315,7 +22313,7 @@
         <v>78</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
@@ -22337,7 +22335,7 @@
         <v>78</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22346,7 +22344,7 @@
         <v>89</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>101</v>
@@ -22398,16 +22396,16 @@
         <v>153</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="N167" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N167" t="s" s="2">
+      <c r="O167" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>78</v>
@@ -22456,7 +22454,7 @@
         <v>78</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22465,7 +22463,7 @@
         <v>80</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ167" t="s" s="2">
         <v>101</v>
@@ -22474,10 +22472,10 @@
         <v>78</v>
       </c>
       <c r="AL167" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM167" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AM167" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>78</v>
@@ -22517,16 +22515,16 @@
         <v>103</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M168" t="s" s="2">
+      <c r="N168" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N168" t="s" s="2">
+      <c r="O168" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>78</v>
@@ -22575,7 +22573,7 @@
         <v>78</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -22584,7 +22582,7 @@
         <v>89</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>101</v>
@@ -22593,10 +22591,10 @@
         <v>78</v>
       </c>
       <c r="AL168" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AM168" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AM168" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>78</v>
@@ -22610,7 +22608,7 @@
         <v>635</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C169" t="s" s="2">
         <v>636</v>
@@ -22635,19 +22633,19 @@
         <v>90</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L169" t="s" s="2">
         <v>637</v>
       </c>
       <c r="M169" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N169" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="N169" t="s" s="2">
+      <c r="O169" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>78</v>
@@ -22672,7 +22670,7 @@
         <v>78</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
@@ -22694,7 +22692,7 @@
         <v>78</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -22712,16 +22710,16 @@
         <v>78</v>
       </c>
       <c r="AL169" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AM169" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AM169" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="170" hidden="true">
@@ -22729,7 +22727,7 @@
         <v>639</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22844,7 +22842,7 @@
         <v>640</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22933,7 +22931,7 @@
         <v>80</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>118</v>
@@ -22959,10 +22957,10 @@
         <v>641</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>78</v>
@@ -22984,13 +22982,13 @@
         <v>78</v>
       </c>
       <c r="K172" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L172" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="L172" t="s" s="2">
+      <c r="M172" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23050,7 +23048,7 @@
         <v>80</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>118</v>
@@ -23076,7 +23074,7 @@
         <v>642</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23191,7 +23189,7 @@
         <v>643</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23280,7 +23278,7 @@
         <v>80</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>118</v>
@@ -23306,7 +23304,7 @@
         <v>644</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23332,13 +23330,13 @@
         <v>136</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M175" t="s" s="2">
+      <c r="N175" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23346,7 +23344,7 @@
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>78</v>
@@ -23388,7 +23386,7 @@
         <v>78</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>89</v>
@@ -23423,7 +23421,7 @@
         <v>645</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23449,10 +23447,10 @@
         <v>175</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>232</v>
+        <v>556</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23479,7 +23477,7 @@
         <v>78</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
@@ -23501,7 +23499,7 @@
         <v>78</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
@@ -23510,7 +23508,7 @@
         <v>89</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>101</v>
@@ -23562,16 +23560,16 @@
         <v>153</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M177" t="s" s="2">
+      <c r="N177" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N177" t="s" s="2">
+      <c r="O177" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>78</v>
@@ -23620,7 +23618,7 @@
         <v>78</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23629,7 +23627,7 @@
         <v>80</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>101</v>
@@ -23638,10 +23636,10 @@
         <v>78</v>
       </c>
       <c r="AL177" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM177" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AM177" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>78</v>
@@ -23681,16 +23679,16 @@
         <v>103</v>
       </c>
       <c r="L178" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M178" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="N178" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N178" t="s" s="2">
+      <c r="O178" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>78</v>
@@ -23739,7 +23737,7 @@
         <v>78</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23748,7 +23746,7 @@
         <v>89</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>101</v>
@@ -23757,10 +23755,10 @@
         <v>78</v>
       </c>
       <c r="AL178" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AM178" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AM178" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>78</v>
@@ -23774,7 +23772,7 @@
         <v>648</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C179" t="s" s="2">
         <v>649</v>
@@ -23799,19 +23797,19 @@
         <v>90</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L179" t="s" s="2">
         <v>650</v>
       </c>
       <c r="M179" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N179" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="N179" t="s" s="2">
+      <c r="O179" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>78</v>
@@ -23839,11 +23837,11 @@
         <v>165</v>
       </c>
       <c r="Y179" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="Z179" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="Z179" t="s" s="2">
-        <v>530</v>
-      </c>
       <c r="AA179" t="s" s="2">
         <v>78</v>
       </c>
@@ -23860,7 +23858,7 @@
         <v>78</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -23878,16 +23876,16 @@
         <v>78</v>
       </c>
       <c r="AL179" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AM179" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AM179" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="180" hidden="true">
@@ -23895,7 +23893,7 @@
         <v>651</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24010,7 +24008,7 @@
         <v>652</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24099,7 +24097,7 @@
         <v>80</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>118</v>
@@ -24125,10 +24123,10 @@
         <v>653</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>78</v>
@@ -24150,13 +24148,13 @@
         <v>78</v>
       </c>
       <c r="K182" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L182" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="L182" t="s" s="2">
+      <c r="M182" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -24216,7 +24214,7 @@
         <v>80</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>118</v>
@@ -24242,7 +24240,7 @@
         <v>654</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24357,7 +24355,7 @@
         <v>655</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24446,7 +24444,7 @@
         <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>118</v>
@@ -24472,7 +24470,7 @@
         <v>656</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24498,13 +24496,13 @@
         <v>136</v>
       </c>
       <c r="L185" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M185" t="s" s="2">
+      <c r="N185" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -24512,7 +24510,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>78</v>
@@ -24554,7 +24552,7 @@
         <v>78</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>89</v>
@@ -24589,7 +24587,7 @@
         <v>657</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24615,10 +24613,10 @@
         <v>175</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>232</v>
+        <v>556</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -24645,7 +24643,7 @@
         <v>78</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
@@ -24667,7 +24665,7 @@
         <v>78</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -24676,7 +24674,7 @@
         <v>89</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>101</v>
@@ -24728,16 +24726,16 @@
         <v>153</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M187" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M187" t="s" s="2">
+      <c r="N187" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N187" t="s" s="2">
+      <c r="O187" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>78</v>
@@ -24786,7 +24784,7 @@
         <v>78</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -24795,7 +24793,7 @@
         <v>80</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>101</v>
@@ -24804,10 +24802,10 @@
         <v>78</v>
       </c>
       <c r="AL187" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM187" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AM187" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>78</v>
@@ -24847,16 +24845,16 @@
         <v>103</v>
       </c>
       <c r="L188" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M188" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M188" t="s" s="2">
+      <c r="N188" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N188" t="s" s="2">
+      <c r="O188" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>78</v>
@@ -24905,7 +24903,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -24914,7 +24912,7 @@
         <v>89</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>101</v>
@@ -24923,10 +24921,10 @@
         <v>78</v>
       </c>
       <c r="AL188" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AM188" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AM188" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>78</v>
@@ -25033,7 +25031,7 @@
         <v>89</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>101</v>
@@ -25700,7 +25698,7 @@
         <v>78</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y195" t="s" s="2">
         <v>697</v>
@@ -25867,7 +25865,7 @@
         <v>711</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>78</v>
@@ -25938,7 +25936,7 @@
         <v>78</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y197" t="s" s="2">
         <v>717</v>
@@ -26137,7 +26135,7 @@
         <v>90</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L199" t="s" s="2">
         <v>730</v>
@@ -26218,7 +26216,7 @@
         <v>733</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>78</v>
@@ -26569,7 +26567,7 @@
         <v>78</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AM202" t="s" s="2">
         <v>755</v>
@@ -26997,7 +26995,7 @@
       </c>
       <c r="Y206" s="2"/>
       <c r="Z206" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>78</v>
@@ -27073,7 +27071,7 @@
         <v>90</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L207" t="s" s="2">
         <v>770</v>
@@ -27670,7 +27668,7 @@
         <v>113</v>
       </c>
       <c r="O212" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>78</v>
@@ -27777,7 +27775,7 @@
         <v>78</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L213" t="s" s="2">
         <v>795</v>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8077" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8078" uniqueCount="821">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T13:43:00+00:00</t>
+    <t>2024-04-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -689,6 +689,9 @@
 </t>
   </si>
   <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
     <t>The date range that this organization should be considered available.</t>
   </si>
   <si>
@@ -738,7 +741,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -778,8 +781,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>dateCreation</t>
@@ -1062,7 +1065,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="IDNST"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1294,7 +1297,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>http://interopsante.org/CodeSystem/fr-v2-0203</t>
+    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1439,7 +1442,7 @@
     <t>Organization.identifier:sirene.system</t>
   </si>
   <si>
-    <t>http://sirene.fr</t>
+    <t>https://sirene.fr</t>
   </si>
   <si>
     <t>Organization.identifier:sirene.value</t>
@@ -1517,7 +1520,7 @@
     <t>Organization.identifier:finess.system</t>
   </si>
   <si>
-    <t>http://finess.esante.gouv.fr</t>
+    <t>https://finess.esante.gouv.fr</t>
   </si>
   <si>
     <t>Organization.identifier:finess.value</t>
@@ -1552,7 +1555,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="INTRN"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1743,9 +1746,6 @@
   </si>
   <si>
     <t>Organization.type.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-organization-types</t>
@@ -5413,10 +5413,10 @@
         <v>214</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5488,7 +5488,7 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5614,14 +5614,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5643,12 +5643,14 @@
         <v>110</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -5706,7 +5708,7 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>118</v>
@@ -5718,7 +5720,7 @@
         <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -5729,10 +5731,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5758,13 +5760,13 @@
         <v>136</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5772,7 +5774,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>78</v>
@@ -5814,7 +5816,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>89</v>
@@ -5846,10 +5848,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5872,13 +5874,13 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5929,7 +5931,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5938,7 +5940,7 @@
         <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>101</v>
@@ -5961,10 +5963,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6076,10 +6078,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6170,7 +6172,7 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>118</v>
@@ -6182,7 +6184,7 @@
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -6193,10 +6195,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6219,16 +6221,16 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6278,7 +6280,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -6287,19 +6289,19 @@
         <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -6310,10 +6312,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6336,23 +6338,23 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>78</v>
@@ -6397,7 +6399,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -6406,19 +6408,19 @@
         <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -6429,13 +6431,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>78</v>
@@ -6457,13 +6459,13 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6546,13 +6548,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>78</v>
@@ -6574,13 +6576,13 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6646,7 +6648,7 @@
         <v>118</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>78</v>
@@ -6663,13 +6665,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>78</v>
@@ -6691,13 +6693,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6780,13 +6782,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>78</v>
@@ -6808,13 +6810,13 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6880,7 +6882,7 @@
         <v>118</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>78</v>
@@ -6897,13 +6899,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>78</v>
@@ -6925,13 +6927,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7014,13 +7016,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>78</v>
@@ -7042,13 +7044,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7131,10 +7133,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7160,16 +7162,16 @@
         <v>110</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -7218,7 +7220,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -7250,10 +7252,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7276,17 +7278,17 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -7323,10 +7325,10 @@
         <v>78</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>78</v>
@@ -7335,7 +7337,7 @@
         <v>116</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -7344,7 +7346,7 @@
         <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>101</v>
@@ -7353,27 +7355,27 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>78</v>
@@ -7395,17 +7397,17 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -7454,7 +7456,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7463,33 +7465,33 @@
         <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7601,10 +7603,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7718,10 +7720,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7747,16 +7749,16 @@
         <v>175</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7766,7 +7768,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7781,13 +7783,13 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -7805,7 +7807,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7826,7 +7828,7 @@
         <v>198</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -7837,10 +7839,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7863,19 +7865,19 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -7885,7 +7887,7 @@
         <v>78</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>78</v>
@@ -7903,10 +7905,10 @@
         <v>157</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
@@ -7924,7 +7926,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7942,10 +7944,10 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -7956,10 +7958,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7985,16 +7987,16 @@
         <v>136</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -8004,10 +8006,10 @@
         <v>78</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>78</v>
@@ -8043,7 +8045,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -8061,13 +8063,13 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -8075,10 +8077,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8104,13 +8106,13 @@
         <v>103</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8124,7 +8126,7 @@
         <v>78</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>78</v>
@@ -8160,7 +8162,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -8178,13 +8180,13 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>78</v>
@@ -8192,10 +8194,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8218,13 +8220,13 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8275,7 +8277,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -8293,13 +8295,13 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -8307,10 +8309,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8333,16 +8335,16 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8392,7 +8394,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8410,13 +8412,13 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
@@ -8424,13 +8426,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>78</v>
@@ -8452,17 +8454,17 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -8511,7 +8513,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8520,33 +8522,33 @@
         <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8658,10 +8660,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8775,10 +8777,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8804,16 +8806,16 @@
         <v>175</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -8838,13 +8840,13 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -8862,7 +8864,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8883,7 +8885,7 @@
         <v>198</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -8894,10 +8896,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8920,19 +8922,19 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -8960,10 +8962,10 @@
         <v>157</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -8981,7 +8983,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8999,10 +9001,10 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -9013,10 +9015,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9128,10 +9130,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9245,10 +9247,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9274,16 +9276,16 @@
         <v>153</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -9332,7 +9334,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9350,10 +9352,10 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -9364,10 +9366,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9479,10 +9481,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9596,10 +9598,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9625,16 +9627,16 @@
         <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -9644,7 +9646,7 @@
         <v>78</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>78</v>
@@ -9683,7 +9685,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9701,10 +9703,10 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -9715,10 +9717,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9744,13 +9746,13 @@
         <v>103</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9800,7 +9802,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9818,10 +9820,10 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -9832,10 +9834,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9861,14 +9863,14 @@
         <v>175</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9917,7 +9919,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9935,10 +9937,10 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -9949,10 +9951,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9978,14 +9980,14 @@
         <v>103</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -10034,7 +10036,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -10052,10 +10054,10 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -10066,10 +10068,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10092,19 +10094,19 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
@@ -10153,7 +10155,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -10171,10 +10173,10 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -10185,10 +10187,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10214,16 +10216,16 @@
         <v>103</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -10272,7 +10274,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -10290,10 +10292,10 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -10304,10 +10306,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10333,16 +10335,16 @@
         <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -10352,10 +10354,10 @@
         <v>78</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>78</v>
@@ -10391,7 +10393,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10409,13 +10411,13 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -10423,10 +10425,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10452,13 +10454,13 @@
         <v>103</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10472,7 +10474,7 @@
         <v>78</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>78</v>
@@ -10508,7 +10510,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10526,13 +10528,13 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -10540,10 +10542,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10566,13 +10568,13 @@
         <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10623,7 +10625,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10641,13 +10643,13 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -10655,10 +10657,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10681,16 +10683,16 @@
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10740,7 +10742,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10758,13 +10760,13 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -10772,13 +10774,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>78</v>
@@ -10800,17 +10802,17 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10859,7 +10861,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10868,33 +10870,33 @@
         <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11006,10 +11008,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11123,10 +11125,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11152,16 +11154,16 @@
         <v>175</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -11186,13 +11188,13 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -11210,7 +11212,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -11231,7 +11233,7 @@
         <v>198</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -11242,10 +11244,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11268,19 +11270,19 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -11308,10 +11310,10 @@
         <v>157</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -11329,7 +11331,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -11347,10 +11349,10 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -11361,10 +11363,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11476,10 +11478,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11593,10 +11595,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11622,16 +11624,16 @@
         <v>153</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -11680,7 +11682,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11698,10 +11700,10 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -11712,10 +11714,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11827,10 +11829,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11944,10 +11946,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11973,16 +11975,16 @@
         <v>136</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11992,7 +11994,7 @@
         <v>78</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>78</v>
@@ -12031,7 +12033,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -12049,10 +12051,10 @@
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -12063,10 +12065,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12092,13 +12094,13 @@
         <v>103</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12148,7 +12150,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -12166,10 +12168,10 @@
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -12180,10 +12182,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12209,14 +12211,14 @@
         <v>175</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -12265,7 +12267,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -12283,10 +12285,10 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -12297,10 +12299,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12326,14 +12328,14 @@
         <v>103</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
@@ -12382,7 +12384,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12400,10 +12402,10 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -12414,10 +12416,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12440,19 +12442,19 @@
         <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -12501,7 +12503,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12519,10 +12521,10 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -12533,10 +12535,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12562,16 +12564,16 @@
         <v>103</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -12620,7 +12622,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12638,10 +12640,10 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>78</v>
@@ -12652,10 +12654,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12681,16 +12683,16 @@
         <v>136</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -12700,10 +12702,10 @@
         <v>78</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>78</v>
@@ -12739,7 +12741,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12757,13 +12759,13 @@
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>78</v>
@@ -12771,10 +12773,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12800,13 +12802,13 @@
         <v>103</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12820,7 +12822,7 @@
         <v>78</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>78</v>
@@ -12856,7 +12858,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12874,13 +12876,13 @@
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>78</v>
@@ -12888,10 +12890,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12914,13 +12916,13 @@
         <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12971,7 +12973,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12989,13 +12991,13 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>78</v>
@@ -13003,10 +13005,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13029,16 +13031,16 @@
         <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13088,7 +13090,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -13106,13 +13108,13 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>78</v>
@@ -13120,13 +13122,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>78</v>
@@ -13148,17 +13150,17 @@
         <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>78</v>
@@ -13207,7 +13209,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -13216,7 +13218,7 @@
         <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>101</v>
@@ -13225,24 +13227,24 @@
         <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13354,10 +13356,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13471,10 +13473,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13500,16 +13502,16 @@
         <v>175</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -13534,13 +13536,13 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -13558,7 +13560,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13579,7 +13581,7 @@
         <v>198</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>78</v>
@@ -13590,10 +13592,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13616,19 +13618,19 @@
         <v>90</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -13638,7 +13640,7 @@
         <v>78</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>78</v>
@@ -13656,10 +13658,10 @@
         <v>157</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -13677,7 +13679,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13695,10 +13697,10 @@
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -13709,10 +13711,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13738,16 +13740,16 @@
         <v>136</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -13757,10 +13759,10 @@
         <v>78</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>78</v>
@@ -13796,7 +13798,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13814,13 +13816,13 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>78</v>
@@ -13828,10 +13830,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13857,13 +13859,13 @@
         <v>103</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13877,7 +13879,7 @@
         <v>78</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>78</v>
@@ -13913,7 +13915,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13931,13 +13933,13 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>78</v>
@@ -13945,10 +13947,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13971,13 +13973,13 @@
         <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14028,7 +14030,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -14046,13 +14048,13 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>78</v>
@@ -14060,10 +14062,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14086,16 +14088,16 @@
         <v>90</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14145,7 +14147,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -14163,13 +14165,13 @@
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>78</v>
@@ -14177,13 +14179,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>78</v>
@@ -14205,17 +14207,17 @@
         <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -14264,7 +14266,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -14273,7 +14275,7 @@
         <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>101</v>
@@ -14282,24 +14284,24 @@
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14411,10 +14413,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14528,10 +14530,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14557,16 +14559,16 @@
         <v>175</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -14591,13 +14593,13 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -14615,7 +14617,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14636,7 +14638,7 @@
         <v>198</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -14647,10 +14649,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14673,19 +14675,19 @@
         <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -14695,7 +14697,7 @@
         <v>78</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>78</v>
@@ -14713,10 +14715,10 @@
         <v>157</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
@@ -14734,7 +14736,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14752,10 +14754,10 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -14766,10 +14768,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14795,16 +14797,16 @@
         <v>136</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -14814,10 +14816,10 @@
         <v>78</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>78</v>
@@ -14853,7 +14855,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14871,13 +14873,13 @@
         <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>78</v>
@@ -14885,10 +14887,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14914,13 +14916,13 @@
         <v>103</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14934,7 +14936,7 @@
         <v>78</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>78</v>
@@ -14970,7 +14972,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14988,13 +14990,13 @@
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>78</v>
@@ -15002,10 +15004,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15028,13 +15030,13 @@
         <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15085,7 +15087,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -15103,13 +15105,13 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>78</v>
@@ -15117,10 +15119,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15143,16 +15145,16 @@
         <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15202,7 +15204,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -15220,13 +15222,13 @@
         <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>78</v>
@@ -15234,10 +15236,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15260,70 +15262,70 @@
         <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q106" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="R106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF106" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q106" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="R106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -15341,24 +15343,24 @@
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15381,19 +15383,19 @@
         <v>90</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -15421,16 +15423,16 @@
         <v>165</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
@@ -15440,7 +15442,7 @@
         <v>116</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -15458,27 +15460,27 @@
         <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>78</v>
@@ -15500,19 +15502,19 @@
         <v>90</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -15537,11 +15539,11 @@
         <v>78</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>78</v>
@@ -15559,7 +15561,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15577,24 +15579,24 @@
         <v>78</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15706,10 +15708,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15821,13 +15823,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="B111" t="s" s="2">
-        <v>541</v>
-      </c>
       <c r="C111" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>78</v>
@@ -15849,13 +15851,13 @@
         <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15938,10 +15940,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16053,10 +16055,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16145,7 +16147,7 @@
         <v>80</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>118</v>
@@ -16168,10 +16170,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16197,13 +16199,13 @@
         <v>136</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16211,7 +16213,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>78</v>
@@ -16253,7 +16255,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>89</v>
@@ -16285,10 +16287,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16314,10 +16316,10 @@
         <v>175</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>556</v>
+        <v>232</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16329,7 +16331,7 @@
         <v>78</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>78</v>
@@ -16344,7 +16346,7 @@
         <v>78</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
@@ -16366,7 +16368,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16375,7 +16377,7 @@
         <v>89</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>101</v>
@@ -16427,16 +16429,16 @@
         <v>153</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -16485,7 +16487,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16503,10 +16505,10 @@
         <v>78</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>78</v>
@@ -16778,16 +16780,16 @@
         <v>136</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>78</v>
@@ -16836,7 +16838,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16854,10 +16856,10 @@
         <v>78</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>78</v>
@@ -16897,13 +16899,13 @@
         <v>103</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16953,7 +16955,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16971,10 +16973,10 @@
         <v>78</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>78</v>
@@ -17017,11 +17019,11 @@
         <v>570</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>78</v>
@@ -17070,7 +17072,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -17088,10 +17090,10 @@
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>78</v>
@@ -17131,14 +17133,14 @@
         <v>103</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -17187,7 +17189,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -17205,10 +17207,10 @@
         <v>78</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>78</v>
@@ -17245,19 +17247,19 @@
         <v>90</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -17306,7 +17308,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17324,10 +17326,10 @@
         <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>78</v>
@@ -17367,16 +17369,16 @@
         <v>103</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -17425,7 +17427,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17443,10 +17445,10 @@
         <v>78</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>78</v>
@@ -17460,7 +17462,7 @@
         <v>577</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>578</v>
@@ -17485,19 +17487,19 @@
         <v>90</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>579</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>78</v>
@@ -17522,7 +17524,7 @@
         <v>78</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
@@ -17544,7 +17546,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17562,16 +17564,16 @@
         <v>78</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="126" hidden="true">
@@ -17579,7 +17581,7 @@
         <v>581</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17694,7 +17696,7 @@
         <v>582</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17837,16 +17839,16 @@
         <v>153</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>78</v>
@@ -17895,7 +17897,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17913,10 +17915,10 @@
         <v>78</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>78</v>
@@ -18188,16 +18190,16 @@
         <v>136</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>78</v>
@@ -18246,7 +18248,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -18264,10 +18266,10 @@
         <v>78</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>78</v>
@@ -18307,13 +18309,13 @@
         <v>103</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18363,7 +18365,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18381,10 +18383,10 @@
         <v>78</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>78</v>
@@ -18427,11 +18429,11 @@
         <v>570</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>78</v>
@@ -18480,7 +18482,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18498,10 +18500,10 @@
         <v>78</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>78</v>
@@ -18541,14 +18543,14 @@
         <v>103</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -18597,7 +18599,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18615,10 +18617,10 @@
         <v>78</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>78</v>
@@ -18655,19 +18657,19 @@
         <v>90</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>78</v>
@@ -18716,7 +18718,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18734,10 +18736,10 @@
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>78</v>
@@ -18777,16 +18779,16 @@
         <v>103</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>78</v>
@@ -18835,7 +18837,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18853,10 +18855,10 @@
         <v>78</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>78</v>
@@ -18870,7 +18872,7 @@
         <v>592</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C137" t="s" s="2">
         <v>593</v>
@@ -18895,19 +18897,19 @@
         <v>90</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L137" t="s" s="2">
         <v>594</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>78</v>
@@ -18932,7 +18934,7 @@
         <v>78</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
@@ -18954,7 +18956,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18972,16 +18974,16 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="138" hidden="true">
@@ -18989,7 +18991,7 @@
         <v>596</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19104,7 +19106,7 @@
         <v>597</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19247,16 +19249,16 @@
         <v>153</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>78</v>
@@ -19305,7 +19307,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19323,10 +19325,10 @@
         <v>78</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>78</v>
@@ -19598,16 +19600,16 @@
         <v>136</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>78</v>
@@ -19656,7 +19658,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19674,10 +19676,10 @@
         <v>78</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>78</v>
@@ -19717,13 +19719,13 @@
         <v>103</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19773,7 +19775,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -19791,10 +19793,10 @@
         <v>78</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>78</v>
@@ -19837,11 +19839,11 @@
         <v>570</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -19890,7 +19892,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -19908,10 +19910,10 @@
         <v>78</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>78</v>
@@ -19951,14 +19953,14 @@
         <v>103</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -20007,7 +20009,7 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -20025,10 +20027,10 @@
         <v>78</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>78</v>
@@ -20065,19 +20067,19 @@
         <v>90</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>78</v>
@@ -20126,7 +20128,7 @@
         <v>78</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -20144,10 +20146,10 @@
         <v>78</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>78</v>
@@ -20187,16 +20189,16 @@
         <v>103</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>78</v>
@@ -20245,7 +20247,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20263,10 +20265,10 @@
         <v>78</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>78</v>
@@ -20280,7 +20282,7 @@
         <v>607</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C149" t="s" s="2">
         <v>608</v>
@@ -20305,19 +20307,19 @@
         <v>90</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L149" t="s" s="2">
         <v>609</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>78</v>
@@ -20342,7 +20344,7 @@
         <v>78</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
@@ -20364,7 +20366,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20382,16 +20384,16 @@
         <v>611</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="150" hidden="true">
@@ -20399,7 +20401,7 @@
         <v>612</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20514,7 +20516,7 @@
         <v>613</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20603,7 +20605,7 @@
         <v>80</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>118</v>
@@ -20629,10 +20631,10 @@
         <v>614</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>78</v>
@@ -20654,13 +20656,13 @@
         <v>78</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -20720,7 +20722,7 @@
         <v>80</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>118</v>
@@ -20746,7 +20748,7 @@
         <v>615</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20861,7 +20863,7 @@
         <v>616</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20950,7 +20952,7 @@
         <v>80</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>118</v>
@@ -20976,7 +20978,7 @@
         <v>617</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21002,13 +21004,13 @@
         <v>136</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21016,7 +21018,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>78</v>
@@ -21058,7 +21060,7 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>89</v>
@@ -21093,7 +21095,7 @@
         <v>618</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21119,10 +21121,10 @@
         <v>175</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>556</v>
+        <v>232</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21149,7 +21151,7 @@
         <v>78</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
@@ -21171,7 +21173,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21180,7 +21182,7 @@
         <v>89</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>101</v>
@@ -21232,16 +21234,16 @@
         <v>153</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>78</v>
@@ -21290,7 +21292,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21299,7 +21301,7 @@
         <v>80</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>101</v>
@@ -21308,10 +21310,10 @@
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>78</v>
@@ -21351,16 +21353,16 @@
         <v>103</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>78</v>
@@ -21409,7 +21411,7 @@
         <v>78</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21418,7 +21420,7 @@
         <v>89</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>101</v>
@@ -21427,10 +21429,10 @@
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>78</v>
@@ -21444,7 +21446,7 @@
         <v>621</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C159" t="s" s="2">
         <v>622</v>
@@ -21469,19 +21471,19 @@
         <v>90</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L159" t="s" s="2">
         <v>623</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
@@ -21506,7 +21508,7 @@
         <v>78</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
@@ -21528,7 +21530,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21546,16 +21548,16 @@
         <v>625</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="160" hidden="true">
@@ -21563,7 +21565,7 @@
         <v>626</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21678,7 +21680,7 @@
         <v>627</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21767,7 +21769,7 @@
         <v>80</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>118</v>
@@ -21793,10 +21795,10 @@
         <v>628</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>78</v>
@@ -21818,13 +21820,13 @@
         <v>78</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -21884,7 +21886,7 @@
         <v>80</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>118</v>
@@ -21910,7 +21912,7 @@
         <v>629</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22025,7 +22027,7 @@
         <v>630</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22114,7 +22116,7 @@
         <v>80</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>118</v>
@@ -22140,7 +22142,7 @@
         <v>631</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22166,13 +22168,13 @@
         <v>136</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22180,7 +22182,7 @@
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>78</v>
@@ -22222,7 +22224,7 @@
         <v>78</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>89</v>
@@ -22257,7 +22259,7 @@
         <v>632</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22283,10 +22285,10 @@
         <v>175</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>556</v>
+        <v>232</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22313,7 +22315,7 @@
         <v>78</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
@@ -22335,7 +22337,7 @@
         <v>78</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22344,7 +22346,7 @@
         <v>89</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>101</v>
@@ -22396,16 +22398,16 @@
         <v>153</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>78</v>
@@ -22454,7 +22456,7 @@
         <v>78</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22463,7 +22465,7 @@
         <v>80</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ167" t="s" s="2">
         <v>101</v>
@@ -22472,10 +22474,10 @@
         <v>78</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>78</v>
@@ -22515,16 +22517,16 @@
         <v>103</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>78</v>
@@ -22573,7 +22575,7 @@
         <v>78</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -22582,7 +22584,7 @@
         <v>89</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>101</v>
@@ -22591,10 +22593,10 @@
         <v>78</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>78</v>
@@ -22608,7 +22610,7 @@
         <v>635</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C169" t="s" s="2">
         <v>636</v>
@@ -22633,19 +22635,19 @@
         <v>90</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L169" t="s" s="2">
         <v>637</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>78</v>
@@ -22670,7 +22672,7 @@
         <v>78</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
@@ -22692,7 +22694,7 @@
         <v>78</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -22710,16 +22712,16 @@
         <v>78</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="170" hidden="true">
@@ -22727,7 +22729,7 @@
         <v>639</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22842,7 +22844,7 @@
         <v>640</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22931,7 +22933,7 @@
         <v>80</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>118</v>
@@ -22957,10 +22959,10 @@
         <v>641</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>78</v>
@@ -22982,13 +22984,13 @@
         <v>78</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23048,7 +23050,7 @@
         <v>80</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>118</v>
@@ -23074,7 +23076,7 @@
         <v>642</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23189,7 +23191,7 @@
         <v>643</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23278,7 +23280,7 @@
         <v>80</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>118</v>
@@ -23304,7 +23306,7 @@
         <v>644</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23330,13 +23332,13 @@
         <v>136</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23344,7 +23346,7 @@
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>78</v>
@@ -23386,7 +23388,7 @@
         <v>78</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>89</v>
@@ -23421,7 +23423,7 @@
         <v>645</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23447,10 +23449,10 @@
         <v>175</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>556</v>
+        <v>232</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23477,7 +23479,7 @@
         <v>78</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
@@ -23499,7 +23501,7 @@
         <v>78</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
@@ -23508,7 +23510,7 @@
         <v>89</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>101</v>
@@ -23560,16 +23562,16 @@
         <v>153</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>78</v>
@@ -23618,7 +23620,7 @@
         <v>78</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23627,7 +23629,7 @@
         <v>80</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>101</v>
@@ -23636,10 +23638,10 @@
         <v>78</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>78</v>
@@ -23679,16 +23681,16 @@
         <v>103</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>78</v>
@@ -23737,7 +23739,7 @@
         <v>78</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23746,7 +23748,7 @@
         <v>89</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>101</v>
@@ -23755,10 +23757,10 @@
         <v>78</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>78</v>
@@ -23772,7 +23774,7 @@
         <v>648</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C179" t="s" s="2">
         <v>649</v>
@@ -23797,19 +23799,19 @@
         <v>90</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L179" t="s" s="2">
         <v>650</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>78</v>
@@ -23837,10 +23839,10 @@
         <v>165</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>78</v>
@@ -23858,7 +23860,7 @@
         <v>78</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -23876,16 +23878,16 @@
         <v>78</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="180" hidden="true">
@@ -23893,7 +23895,7 @@
         <v>651</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24008,7 +24010,7 @@
         <v>652</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24097,7 +24099,7 @@
         <v>80</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>118</v>
@@ -24123,10 +24125,10 @@
         <v>653</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>78</v>
@@ -24148,13 +24150,13 @@
         <v>78</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -24214,7 +24216,7 @@
         <v>80</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>118</v>
@@ -24240,7 +24242,7 @@
         <v>654</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24355,7 +24357,7 @@
         <v>655</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24444,7 +24446,7 @@
         <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>118</v>
@@ -24470,7 +24472,7 @@
         <v>656</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24496,13 +24498,13 @@
         <v>136</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -24510,7 +24512,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>78</v>
@@ -24552,7 +24554,7 @@
         <v>78</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>89</v>
@@ -24587,7 +24589,7 @@
         <v>657</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24613,10 +24615,10 @@
         <v>175</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>556</v>
+        <v>232</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -24643,7 +24645,7 @@
         <v>78</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
@@ -24665,7 +24667,7 @@
         <v>78</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -24674,7 +24676,7 @@
         <v>89</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>101</v>
@@ -24726,16 +24728,16 @@
         <v>153</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>78</v>
@@ -24784,7 +24786,7 @@
         <v>78</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -24793,7 +24795,7 @@
         <v>80</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>101</v>
@@ -24802,10 +24804,10 @@
         <v>78</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>78</v>
@@ -24845,16 +24847,16 @@
         <v>103</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>78</v>
@@ -24903,7 +24905,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -24912,7 +24914,7 @@
         <v>89</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>101</v>
@@ -24921,10 +24923,10 @@
         <v>78</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>78</v>
@@ -25031,7 +25033,7 @@
         <v>89</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>101</v>
@@ -25698,7 +25700,7 @@
         <v>78</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y195" t="s" s="2">
         <v>697</v>
@@ -25865,7 +25867,7 @@
         <v>711</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>78</v>
@@ -25936,7 +25938,7 @@
         <v>78</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y197" t="s" s="2">
         <v>717</v>
@@ -26135,7 +26137,7 @@
         <v>90</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L199" t="s" s="2">
         <v>730</v>
@@ -26216,7 +26218,7 @@
         <v>733</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>78</v>
@@ -26567,7 +26569,7 @@
         <v>78</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AM202" t="s" s="2">
         <v>755</v>
@@ -26995,7 +26997,7 @@
       </c>
       <c r="Y206" s="2"/>
       <c r="Z206" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>78</v>
@@ -27071,7 +27073,7 @@
         <v>90</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L207" t="s" s="2">
         <v>770</v>
@@ -27668,7 +27670,7 @@
         <v>113</v>
       </c>
       <c r="O212" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>78</v>
@@ -27775,7 +27777,7 @@
         <v>78</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L213" t="s" s="2">
         <v>795</v>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$222</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8077" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8257" uniqueCount="828">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T08:44:23+00:00</t>
+    <t>2024-07-10T09:54:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -789,7 +789,7 @@
 per-1</t>
   </si>
   <si>
-    <t>dateCreation</t>
+    <t>EntiteJuridique.dateCreation</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -819,7 +819,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>dateFermeture</t>
+    <t>EntiteJuridique.dateFermeture</t>
   </si>
   <si>
     <t>DR.2</t>
@@ -860,7 +860,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la licence d’exploitation d’une officine.</t>
   </si>
   <si>
-    <t>numeroLicenceOfficine</t>
+    <t>EntiteJuridique.numeroLicenceOfficine</t>
   </si>
   <si>
     <t>Organization.extension:as-ext-organization-pricing-model</t>
@@ -895,7 +895,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte du type de fermeture de la structure.</t>
   </si>
   <si>
-    <t>typeFermeture</t>
+    <t>EntiteJuridique.typeFermeture</t>
   </si>
   <si>
     <t>Organization.extension:as-ext-organization-budget-type</t>
@@ -994,7 +994,7 @@
     <t>Identifiant idNat_Struct délivré par une autorité d'enregistrement tel que défini dans l'Annexe Transverse Source des données métier pour les professionnels et les structures.</t>
   </si>
   <si>
-    <t>idNat_struct</t>
+    <t>EntiteJuridique.idNat_struct</t>
   </si>
   <si>
     <t>Organization.identifier:idNatSt.id</t>
@@ -1217,7 +1217,7 @@
     <t>Identifiant SIREN (9 chiffres) ou SIRET (14 chiffres)</t>
   </si>
   <si>
-    <t>numSiren</t>
+    <t>EntiteJuridique.numSiren</t>
   </si>
   <si>
     <t>Organization.identifier:sirene.id</t>
@@ -1470,7 +1470,7 @@
     <t>Identifiant FINESS Entité Géographique (EG) ou Entité Juridique (EJ)</t>
   </si>
   <si>
-    <t>numFiness</t>
+    <t>EntiteJuridique.numFiness</t>
   </si>
   <si>
     <t>Organization.identifier:finess.id</t>
@@ -1833,6 +1833,21 @@
     <t>Organization.type:secteurActiviteRASS.extension</t>
   </si>
   <si>
+    <t>Organization.type:secteurActiviteRASS.extension:as-ext-organization-types</t>
+  </si>
+  <si>
+    <t>Organization.type:secteurActiviteRASS.extension:as-ext-organization-types.id</t>
+  </si>
+  <si>
+    <t>Organization.type:secteurActiviteRASS.extension:as-ext-organization-types.extension</t>
+  </si>
+  <si>
+    <t>Organization.type:secteurActiviteRASS.extension:as-ext-organization-types.url</t>
+  </si>
+  <si>
+    <t>Organization.type:secteurActiviteRASS.extension:as-ext-organization-types.value[x]</t>
+  </si>
+  <si>
     <t>Organization.type:secteurActiviteRASS.coding</t>
   </si>
   <si>
@@ -1918,7 +1933,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J99-InseeNAFrav2Niveau5-RASS/FHIR/JDV-J99-InseeNAFrav2Niveau5-RASS</t>
   </si>
   <si>
-    <t>codeAPEN</t>
+    <t>EntiteJuridique.codeAPEN</t>
   </si>
   <si>
     <t>Organization.type:activiteINSEE.id</t>
@@ -1960,7 +1975,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J100-FinessStatutJuridique-RASS/FHIR/JDV-J100-FinessStatutJuridique-RASS</t>
   </si>
   <si>
-    <t>statutJuridique</t>
+    <t>EntiteJuridique.statutJuridique</t>
   </si>
   <si>
     <t>Organization.type:statutJuridiqueINSEE.id</t>
@@ -2080,7 +2095,7 @@
     <t>Need to use the name as the label of the organization.</t>
   </si>
   <si>
-    <t>raisonSociale</t>
+    <t>EntiteJuridique.raisonSociale</t>
   </si>
   <si>
     <t>XON.1</t>
@@ -2108,7 +2123,7 @@
 For searching knowing previous names that the organization was known by can be very useful.</t>
   </si>
   <si>
-    <t>raisonSocialeLongue</t>
+    <t>EntiteJuridique.raisonSocialeLongue</t>
   </si>
   <si>
     <t>Organization.telecom</t>
@@ -2138,7 +2153,7 @@
 ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}org-3:The telecom of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
   </si>
   <si>
-    <t>telecommunication</t>
+    <t>EntiteJuridique.telecommunication</t>
   </si>
   <si>
     <t>XTN</t>
@@ -2307,7 +2322,7 @@
     <t>Les BALs MSS de type ORG ou APP rattachées à une personne morale responsable de l’accès et de l’usage de la BAL (boiteLettreMSS).</t>
   </si>
   <si>
-    <t>boiteLettreMSS</t>
+    <t>EntiteJuridique.boiteLettreMSS</t>
   </si>
   <si>
     <t>Organization.address</t>
@@ -2333,7 +2348,7 @@
 org-2:An address of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
   </si>
   <si>
-    <t>adresseEJ</t>
+    <t>EntiteJuridique.adresseEJ</t>
   </si>
   <si>
     <t>XAD</t>
@@ -2885,7 +2900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO217"/>
+  <dimension ref="A1:AO222"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="80.17578125" customWidth="true" bestFit="true"/>
@@ -17705,11 +17720,11 @@
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>80</v>
@@ -17727,14 +17742,12 @@
         <v>110</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>111</v>
+        <v>200</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>78</v>
@@ -17804,7 +17817,7 @@
         <v>78</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>78</v>
@@ -17818,9 +17831,11 @@
         <v>585</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="C128" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="D128" t="s" s="2">
         <v>78</v>
       </c>
@@ -17838,23 +17853,19 @@
         <v>78</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>153</v>
+        <v>546</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>395</v>
+        <v>547</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>78</v>
       </c>
@@ -17902,7 +17913,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>399</v>
+        <v>117</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17914,16 +17925,16 @@
         <v>78</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>401</v>
+        <v>78</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>78</v>
@@ -17937,7 +17948,7 @@
         <v>586</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18052,18 +18063,18 @@
         <v>587</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>78</v>
@@ -18078,14 +18089,12 @@
         <v>110</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>111</v>
+        <v>200</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>78</v>
@@ -18143,7 +18152,7 @@
         <v>80</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>118</v>
@@ -18155,7 +18164,7 @@
         <v>78</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>78</v>
@@ -18169,7 +18178,7 @@
         <v>588</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18189,29 +18198,27 @@
         <v>78</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K131" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>409</v>
+        <v>224</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>78</v>
+        <v>555</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>78</v>
@@ -18253,10 +18260,10 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>413</v>
+        <v>227</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>89</v>
@@ -18265,16 +18272,16 @@
         <v>78</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>414</v>
+        <v>78</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>415</v>
+        <v>198</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>78</v>
@@ -18288,7 +18295,7 @@
         <v>589</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18308,20 +18315,18 @@
         <v>78</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>418</v>
+        <v>231</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>78</v>
@@ -18331,7 +18336,7 @@
         <v>78</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>78</v>
+        <v>580</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>78</v>
@@ -18346,13 +18351,11 @@
         <v>78</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>78</v>
+        <v>559</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>78</v>
@@ -18370,7 +18373,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>421</v>
+        <v>233</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18379,7 +18382,7 @@
         <v>89</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>101</v>
@@ -18388,10 +18391,10 @@
         <v>78</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>422</v>
+        <v>78</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>423</v>
+        <v>198</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>78</v>
@@ -18405,7 +18408,7 @@
         <v>590</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18413,7 +18416,7 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G133" t="s" s="2">
         <v>89</v>
@@ -18428,17 +18431,19 @@
         <v>90</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>572</v>
+        <v>395</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N133" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="O133" t="s" s="2">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>78</v>
@@ -18487,13 +18492,13 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>78</v>
@@ -18505,10 +18510,10 @@
         <v>78</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>78</v>
@@ -18522,7 +18527,7 @@
         <v>591</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18542,21 +18547,19 @@
         <v>78</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K134" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>434</v>
+        <v>104</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>435</v>
+        <v>105</v>
       </c>
       <c r="N134" s="2"/>
-      <c r="O134" t="s" s="2">
-        <v>436</v>
-      </c>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>78</v>
       </c>
@@ -18604,7 +18607,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>437</v>
+        <v>106</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18616,16 +18619,16 @@
         <v>78</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>438</v>
+        <v>78</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>439</v>
+        <v>107</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>78</v>
@@ -18639,18 +18642,18 @@
         <v>592</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>78</v>
@@ -18659,23 +18662,21 @@
         <v>78</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>442</v>
+        <v>110</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>443</v>
+        <v>111</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>444</v>
+        <v>112</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>78</v>
       </c>
@@ -18711,40 +18712,40 @@
         <v>78</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC135" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD135" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>447</v>
+        <v>117</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>449</v>
+        <v>107</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>78</v>
@@ -18758,7 +18759,7 @@
         <v>593</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18766,7 +18767,7 @@
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G136" t="s" s="2">
         <v>89</v>
@@ -18781,19 +18782,19 @@
         <v>90</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>452</v>
+        <v>408</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>453</v>
+        <v>409</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>454</v>
+        <v>410</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>455</v>
+        <v>411</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>78</v>
@@ -18842,7 +18843,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>456</v>
+        <v>413</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18860,10 +18861,10 @@
         <v>78</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>457</v>
+        <v>414</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>458</v>
+        <v>415</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>78</v>
@@ -18877,11 +18878,9 @@
         <v>594</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C137" t="s" s="2">
-        <v>595</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
         <v>78</v>
       </c>
@@ -18902,20 +18901,18 @@
         <v>90</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>331</v>
+        <v>103</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>596</v>
+        <v>418</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>527</v>
+        <v>419</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>78</v>
       </c>
@@ -18939,11 +18936,13 @@
         <v>78</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y137" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z137" t="s" s="2">
-        <v>597</v>
+        <v>78</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>78</v>
@@ -18961,13 +18960,13 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>525</v>
+        <v>421</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>78</v>
@@ -18979,24 +18978,24 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>533</v>
+        <v>422</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>534</v>
+        <v>423</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>541</v>
+        <v>571</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19016,19 +19015,21 @@
         <v>78</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>104</v>
+        <v>572</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>105</v>
+        <v>427</v>
       </c>
       <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
+      <c r="O138" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>78</v>
       </c>
@@ -19076,7 +19077,7 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>106</v>
+        <v>429</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -19088,16 +19089,16 @@
         <v>78</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>78</v>
+        <v>430</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>107</v>
+        <v>431</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>78</v>
@@ -19108,21 +19109,21 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>543</v>
+        <v>574</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>78</v>
@@ -19131,21 +19132,21 @@
         <v>78</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>111</v>
+        <v>434</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O139" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P139" t="s" s="2">
         <v>78</v>
       </c>
@@ -19181,40 +19182,40 @@
         <v>78</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC139" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD139" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>117</v>
+        <v>437</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>78</v>
+        <v>438</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>107</v>
+        <v>439</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>78</v>
@@ -19225,10 +19226,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19236,7 +19237,7 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G140" t="s" s="2">
         <v>89</v>
@@ -19251,19 +19252,19 @@
         <v>90</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>153</v>
+        <v>442</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>395</v>
+        <v>443</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>396</v>
+        <v>444</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>397</v>
+        <v>445</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>398</v>
+        <v>446</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>78</v>
@@ -19312,13 +19313,13 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>399</v>
+        <v>447</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>78</v>
@@ -19330,10 +19331,10 @@
         <v>78</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>400</v>
+        <v>448</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>401</v>
+        <v>449</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>78</v>
@@ -19344,10 +19345,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>563</v>
+        <v>578</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19367,19 +19368,23 @@
         <v>78</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K141" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>104</v>
+        <v>452</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>78</v>
       </c>
@@ -19427,7 +19432,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>106</v>
+        <v>456</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19439,16 +19444,16 @@
         <v>78</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>107</v>
+        <v>458</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>78</v>
@@ -19459,21 +19464,23 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="C142" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>600</v>
+      </c>
       <c r="D142" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>78</v>
@@ -19482,21 +19489,23 @@
         <v>78</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>110</v>
+        <v>331</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>111</v>
+        <v>601</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>112</v>
+        <v>527</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O142" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
       </c>
@@ -19520,31 +19529,29 @@
         <v>78</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>78</v>
+        <v>602</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>117</v>
+        <v>525</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19556,22 +19563,22 @@
         <v>78</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AM142" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AN142" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="AN142" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AO142" t="s" s="2">
-        <v>78</v>
+        <v>535</v>
       </c>
     </row>
     <row r="143" hidden="true">
@@ -19579,7 +19586,7 @@
         <v>603</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>567</v>
+        <v>541</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19587,7 +19594,7 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G143" t="s" s="2">
         <v>89</v>
@@ -19599,23 +19606,19 @@
         <v>78</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>408</v>
+        <v>104</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N143" s="2"/>
+      <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>78</v>
       </c>
@@ -19663,7 +19666,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>413</v>
+        <v>106</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19675,16 +19678,16 @@
         <v>78</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>414</v>
+        <v>78</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>415</v>
+        <v>107</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>78</v>
@@ -19698,18 +19701,18 @@
         <v>604</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>569</v>
+        <v>543</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>78</v>
@@ -19718,19 +19721,19 @@
         <v>78</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>418</v>
+        <v>111</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>419</v>
+        <v>112</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>420</v>
+        <v>113</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19768,40 +19771,40 @@
         <v>78</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC144" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD144" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>421</v>
+        <v>117</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>422</v>
+        <v>78</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>423</v>
+        <v>107</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>78</v>
@@ -19815,7 +19818,7 @@
         <v>605</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19823,7 +19826,7 @@
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G145" t="s" s="2">
         <v>89</v>
@@ -19838,17 +19841,19 @@
         <v>90</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>572</v>
+        <v>395</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N145" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="O145" t="s" s="2">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -19897,13 +19902,13 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>78</v>
@@ -19915,10 +19920,10 @@
         <v>78</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>78</v>
@@ -19932,7 +19937,7 @@
         <v>606</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19952,21 +19957,19 @@
         <v>78</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K146" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>434</v>
+        <v>104</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>435</v>
+        <v>105</v>
       </c>
       <c r="N146" s="2"/>
-      <c r="O146" t="s" s="2">
-        <v>436</v>
-      </c>
+      <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>78</v>
       </c>
@@ -20014,7 +20017,7 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>437</v>
+        <v>106</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -20026,16 +20029,16 @@
         <v>78</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>438</v>
+        <v>78</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>439</v>
+        <v>107</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>78</v>
@@ -20049,18 +20052,18 @@
         <v>607</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>78</v>
@@ -20069,23 +20072,21 @@
         <v>78</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>442</v>
+        <v>110</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>443</v>
+        <v>111</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>444</v>
+        <v>112</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>78</v>
       </c>
@@ -20121,40 +20122,40 @@
         <v>78</v>
       </c>
       <c r="AB147" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC147" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD147" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE147" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>447</v>
+        <v>117</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>449</v>
+        <v>107</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>78</v>
@@ -20168,7 +20169,7 @@
         <v>608</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20176,7 +20177,7 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>89</v>
@@ -20191,19 +20192,19 @@
         <v>90</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>452</v>
+        <v>408</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>453</v>
+        <v>409</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>454</v>
+        <v>410</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>455</v>
+        <v>411</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>78</v>
@@ -20252,7 +20253,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>456</v>
+        <v>413</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20270,10 +20271,10 @@
         <v>78</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>457</v>
+        <v>414</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>458</v>
+        <v>415</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>78</v>
@@ -20287,11 +20288,9 @@
         <v>609</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C149" t="s" s="2">
-        <v>610</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
         <v>78</v>
       </c>
@@ -20312,20 +20311,18 @@
         <v>90</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>331</v>
+        <v>103</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>611</v>
+        <v>418</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>527</v>
+        <v>419</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>78</v>
       </c>
@@ -20349,11 +20346,13 @@
         <v>78</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y149" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z149" t="s" s="2">
-        <v>612</v>
+        <v>78</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>78</v>
@@ -20371,13 +20370,13 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>525</v>
+        <v>421</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>78</v>
@@ -20386,27 +20385,27 @@
         <v>101</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>613</v>
+        <v>78</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>533</v>
+        <v>422</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>534</v>
+        <v>423</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>541</v>
+        <v>571</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20426,19 +20425,21 @@
         <v>78</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>104</v>
+        <v>572</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>105</v>
+        <v>427</v>
       </c>
       <c r="N150" s="2"/>
-      <c r="O150" s="2"/>
+      <c r="O150" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P150" t="s" s="2">
         <v>78</v>
       </c>
@@ -20486,7 +20487,7 @@
         <v>78</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>106</v>
+        <v>429</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20498,16 +20499,16 @@
         <v>78</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK150" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>78</v>
+        <v>430</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>107</v>
+        <v>431</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>78</v>
@@ -20518,10 +20519,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>543</v>
+        <v>574</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20529,10 +20530,10 @@
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>78</v>
@@ -20541,19 +20542,21 @@
         <v>78</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>200</v>
+        <v>434</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>201</v>
+        <v>435</v>
       </c>
       <c r="N151" s="2"/>
-      <c r="O151" s="2"/>
+      <c r="O151" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P151" t="s" s="2">
         <v>78</v>
       </c>
@@ -20589,40 +20592,40 @@
         <v>78</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC151" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD151" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE151" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>117</v>
+        <v>437</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>78</v>
+        <v>438</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>78</v>
@@ -20633,20 +20636,18 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C152" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G152" t="s" s="2">
         <v>89</v>
@@ -20658,19 +20659,23 @@
         <v>78</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>546</v>
+        <v>442</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>547</v>
+        <v>443</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N152" s="2"/>
-      <c r="O152" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O152" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P152" t="s" s="2">
         <v>78</v>
       </c>
@@ -20718,28 +20723,28 @@
         <v>78</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>117</v>
+        <v>447</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>78</v>
+        <v>448</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>78</v>
+        <v>449</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>78</v>
@@ -20750,10 +20755,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20773,19 +20778,23 @@
         <v>78</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K153" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>104</v>
+        <v>452</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N153" s="2"/>
-      <c r="O153" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O153" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P153" t="s" s="2">
         <v>78</v>
       </c>
@@ -20833,7 +20842,7 @@
         <v>78</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>106</v>
+        <v>456</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -20845,16 +20854,16 @@
         <v>78</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>107</v>
+        <v>458</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>78</v>
@@ -20865,12 +20874,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C154" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="C154" t="s" s="2">
+        <v>615</v>
+      </c>
       <c r="D154" t="s" s="2">
         <v>78</v>
       </c>
@@ -20879,7 +20890,7 @@
         <v>79</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>78</v>
@@ -20888,19 +20899,23 @@
         <v>78</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>110</v>
+        <v>331</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>200</v>
+        <v>616</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N154" s="2"/>
-      <c r="O154" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O154" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P154" t="s" s="2">
         <v>78</v>
       </c>
@@ -20924,31 +20939,29 @@
         <v>78</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y154" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y154" s="2"/>
       <c r="Z154" t="s" s="2">
-        <v>78</v>
+        <v>617</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>117</v>
+        <v>525</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -20957,25 +20970,25 @@
         <v>80</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>78</v>
+        <v>618</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>78</v>
+        <v>534</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>78</v>
+        <v>535</v>
       </c>
     </row>
     <row r="155" hidden="true">
@@ -20983,7 +20996,7 @@
         <v>619</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20991,7 +21004,7 @@
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G155" t="s" s="2">
         <v>89</v>
@@ -21006,24 +21019,22 @@
         <v>78</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>223</v>
+        <v>104</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N155" s="2"/>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>555</v>
+        <v>78</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>78</v>
@@ -21065,10 +21076,10 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>227</v>
+        <v>106</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>89</v>
@@ -21086,7 +21097,7 @@
         <v>78</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>78</v>
@@ -21100,7 +21111,7 @@
         <v>620</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21108,10 +21119,10 @@
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>78</v>
@@ -21123,13 +21134,13 @@
         <v>78</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>558</v>
+        <v>201</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21141,7 +21152,7 @@
         <v>78</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>610</v>
+        <v>78</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>78</v>
@@ -21156,41 +21167,43 @@
         <v>78</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y156" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z156" t="s" s="2">
-        <v>559</v>
+        <v>78</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>233</v>
+        <v>117</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>78</v>
@@ -21199,7 +21212,7 @@
         <v>78</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>78</v>
@@ -21213,18 +21226,20 @@
         <v>621</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="C157" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="C157" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="D157" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>78</v>
@@ -21233,23 +21248,19 @@
         <v>78</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>153</v>
+        <v>546</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>395</v>
+        <v>547</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N157" s="2"/>
+      <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>78</v>
       </c>
@@ -21297,7 +21308,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>399</v>
+        <v>117</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21309,16 +21320,16 @@
         <v>207</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>401</v>
+        <v>78</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>78</v>
@@ -21332,7 +21343,7 @@
         <v>622</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>578</v>
+        <v>550</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21352,23 +21363,19 @@
         <v>78</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K158" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>452</v>
+        <v>104</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N158" s="2"/>
+      <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>78</v>
       </c>
@@ -21416,7 +21423,7 @@
         <v>78</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>456</v>
+        <v>106</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21425,19 +21432,19 @@
         <v>89</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>457</v>
+        <v>78</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>458</v>
+        <v>107</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>78</v>
@@ -21451,11 +21458,9 @@
         <v>623</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C159" t="s" s="2">
-        <v>624</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
         <v>78</v>
       </c>
@@ -21464,7 +21469,7 @@
         <v>79</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>78</v>
@@ -21473,23 +21478,19 @@
         <v>78</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>331</v>
+        <v>110</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>625</v>
+        <v>200</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N159" s="2"/>
+      <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>78</v>
       </c>
@@ -21513,29 +21514,31 @@
         <v>78</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y159" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z159" t="s" s="2">
-        <v>626</v>
+        <v>78</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB159" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC159" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD159" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE159" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>525</v>
+        <v>117</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21544,33 +21547,33 @@
         <v>80</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>627</v>
+        <v>78</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>533</v>
+        <v>78</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21578,7 +21581,7 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G160" t="s" s="2">
         <v>89</v>
@@ -21593,22 +21596,24 @@
         <v>78</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>104</v>
+        <v>223</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N160" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q160" s="2"/>
       <c r="R160" t="s" s="2">
-        <v>78</v>
+        <v>555</v>
       </c>
       <c r="S160" t="s" s="2">
         <v>78</v>
@@ -21650,10 +21655,10 @@
         <v>78</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>106</v>
+        <v>227</v>
       </c>
       <c r="AG160" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH160" t="s" s="2">
         <v>89</v>
@@ -21671,7 +21676,7 @@
         <v>78</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>78</v>
@@ -21682,10 +21687,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21693,10 +21698,10 @@
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>78</v>
@@ -21708,13 +21713,13 @@
         <v>78</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>201</v>
+        <v>558</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -21726,7 +21731,7 @@
         <v>78</v>
       </c>
       <c r="S161" t="s" s="2">
-        <v>78</v>
+        <v>615</v>
       </c>
       <c r="T161" t="s" s="2">
         <v>78</v>
@@ -21741,43 +21746,41 @@
         <v>78</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y161" s="2"/>
       <c r="Z161" t="s" s="2">
-        <v>78</v>
+        <v>559</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB161" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC161" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD161" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE161" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>117</v>
+        <v>233</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>78</v>
@@ -21786,7 +21789,7 @@
         <v>78</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>78</v>
@@ -21797,23 +21800,21 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C162" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H162" t="s" s="2">
         <v>78</v>
@@ -21822,19 +21823,23 @@
         <v>78</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>546</v>
+        <v>153</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>547</v>
+        <v>395</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N162" s="2"/>
-      <c r="O162" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N162" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O162" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P162" t="s" s="2">
         <v>78</v>
       </c>
@@ -21882,7 +21887,7 @@
         <v>78</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>117</v>
+        <v>399</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -21894,16 +21899,16 @@
         <v>207</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK162" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>78</v>
@@ -21914,10 +21919,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21937,19 +21942,23 @@
         <v>78</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K163" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>104</v>
+        <v>452</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N163" s="2"/>
-      <c r="O163" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P163" t="s" s="2">
         <v>78</v>
       </c>
@@ -21997,7 +22006,7 @@
         <v>78</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>106</v>
+        <v>456</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -22006,19 +22015,19 @@
         <v>89</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>107</v>
+        <v>458</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>78</v>
@@ -22029,12 +22038,14 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C164" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="C164" t="s" s="2">
+        <v>629</v>
+      </c>
       <c r="D164" t="s" s="2">
         <v>78</v>
       </c>
@@ -22043,7 +22054,7 @@
         <v>79</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>78</v>
@@ -22052,19 +22063,23 @@
         <v>78</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>110</v>
+        <v>331</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>200</v>
+        <v>630</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N164" s="2"/>
-      <c r="O164" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>78</v>
       </c>
@@ -22088,31 +22103,29 @@
         <v>78</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y164" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>78</v>
+        <v>631</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB164" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC164" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD164" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE164" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>117</v>
+        <v>525</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -22121,25 +22134,25 @@
         <v>80</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>78</v>
+        <v>632</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>78</v>
+        <v>534</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>78</v>
+        <v>535</v>
       </c>
     </row>
     <row r="165" hidden="true">
@@ -22147,7 +22160,7 @@
         <v>633</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22155,7 +22168,7 @@
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G165" t="s" s="2">
         <v>89</v>
@@ -22170,24 +22183,22 @@
         <v>78</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>223</v>
+        <v>104</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N165" s="2"/>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>555</v>
+        <v>78</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>78</v>
@@ -22229,10 +22240,10 @@
         <v>78</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>227</v>
+        <v>106</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>89</v>
@@ -22250,7 +22261,7 @@
         <v>78</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>78</v>
@@ -22264,7 +22275,7 @@
         <v>634</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22272,10 +22283,10 @@
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>78</v>
@@ -22287,13 +22298,13 @@
         <v>78</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>558</v>
+        <v>201</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22305,7 +22316,7 @@
         <v>78</v>
       </c>
       <c r="S166" t="s" s="2">
-        <v>624</v>
+        <v>78</v>
       </c>
       <c r="T166" t="s" s="2">
         <v>78</v>
@@ -22320,41 +22331,43 @@
         <v>78</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y166" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z166" t="s" s="2">
-        <v>559</v>
+        <v>78</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE166" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>233</v>
+        <v>117</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>78</v>
@@ -22363,7 +22376,7 @@
         <v>78</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>78</v>
@@ -22377,18 +22390,20 @@
         <v>635</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="C167" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="C167" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="D167" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>78</v>
@@ -22397,23 +22412,19 @@
         <v>78</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>153</v>
+        <v>546</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>395</v>
+        <v>547</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N167" s="2"/>
+      <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>78</v>
       </c>
@@ -22461,7 +22472,7 @@
         <v>78</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>399</v>
+        <v>117</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22473,16 +22484,16 @@
         <v>207</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>401</v>
+        <v>78</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>78</v>
@@ -22496,7 +22507,7 @@
         <v>636</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>578</v>
+        <v>550</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22516,23 +22527,19 @@
         <v>78</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K168" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>452</v>
+        <v>104</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N168" s="2"/>
+      <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>78</v>
       </c>
@@ -22580,7 +22587,7 @@
         <v>78</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>456</v>
+        <v>106</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -22589,19 +22596,19 @@
         <v>89</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>457</v>
+        <v>78</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>458</v>
+        <v>107</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>78</v>
@@ -22615,11 +22622,9 @@
         <v>637</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C169" t="s" s="2">
-        <v>638</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
         <v>78</v>
       </c>
@@ -22628,7 +22633,7 @@
         <v>79</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>78</v>
@@ -22637,23 +22642,19 @@
         <v>78</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>331</v>
+        <v>110</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>639</v>
+        <v>200</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N169" s="2"/>
+      <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>78</v>
       </c>
@@ -22677,29 +22678,31 @@
         <v>78</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y169" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y169" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z169" t="s" s="2">
-        <v>640</v>
+        <v>78</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>525</v>
+        <v>117</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -22708,33 +22711,33 @@
         <v>80</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>533</v>
+        <v>78</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22742,7 +22745,7 @@
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G170" t="s" s="2">
         <v>89</v>
@@ -22757,22 +22760,24 @@
         <v>78</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>104</v>
+        <v>223</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N170" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N170" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q170" s="2"/>
       <c r="R170" t="s" s="2">
-        <v>78</v>
+        <v>555</v>
       </c>
       <c r="S170" t="s" s="2">
         <v>78</v>
@@ -22814,10 +22819,10 @@
         <v>78</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>106</v>
+        <v>227</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>89</v>
@@ -22835,7 +22840,7 @@
         <v>78</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>78</v>
@@ -22846,10 +22851,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22857,10 +22862,10 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>78</v>
@@ -22872,13 +22877,13 @@
         <v>78</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>201</v>
+        <v>558</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -22890,7 +22895,7 @@
         <v>78</v>
       </c>
       <c r="S171" t="s" s="2">
-        <v>78</v>
+        <v>629</v>
       </c>
       <c r="T171" t="s" s="2">
         <v>78</v>
@@ -22905,43 +22910,41 @@
         <v>78</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y171" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y171" s="2"/>
       <c r="Z171" t="s" s="2">
-        <v>78</v>
+        <v>559</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB171" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC171" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD171" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE171" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>117</v>
+        <v>233</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI171" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>78</v>
@@ -22950,7 +22953,7 @@
         <v>78</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>78</v>
@@ -22961,23 +22964,21 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C172" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>78</v>
@@ -22986,19 +22987,23 @@
         <v>78</v>
       </c>
       <c r="J172" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>546</v>
+        <v>153</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>547</v>
+        <v>395</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N172" s="2"/>
-      <c r="O172" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O172" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P172" t="s" s="2">
         <v>78</v>
       </c>
@@ -23046,7 +23051,7 @@
         <v>78</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>117</v>
+        <v>399</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -23058,16 +23063,16 @@
         <v>207</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="AN172" t="s" s="2">
         <v>78</v>
@@ -23078,10 +23083,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23101,19 +23106,23 @@
         <v>78</v>
       </c>
       <c r="J173" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K173" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>104</v>
+        <v>452</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N173" s="2"/>
-      <c r="O173" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O173" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P173" t="s" s="2">
         <v>78</v>
       </c>
@@ -23161,7 +23170,7 @@
         <v>78</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>106</v>
+        <v>456</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -23170,19 +23179,19 @@
         <v>89</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>107</v>
+        <v>458</v>
       </c>
       <c r="AN173" t="s" s="2">
         <v>78</v>
@@ -23193,12 +23202,14 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C174" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="C174" t="s" s="2">
+        <v>643</v>
+      </c>
       <c r="D174" t="s" s="2">
         <v>78</v>
       </c>
@@ -23207,7 +23218,7 @@
         <v>79</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>78</v>
@@ -23216,19 +23227,23 @@
         <v>78</v>
       </c>
       <c r="J174" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>110</v>
+        <v>331</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>200</v>
+        <v>644</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N174" s="2"/>
-      <c r="O174" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O174" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P174" t="s" s="2">
         <v>78</v>
       </c>
@@ -23252,31 +23267,29 @@
         <v>78</v>
       </c>
       <c r="X174" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y174" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y174" s="2"/>
       <c r="Z174" t="s" s="2">
-        <v>78</v>
+        <v>645</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB174" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC174" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD174" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE174" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>117</v>
+        <v>525</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>79</v>
@@ -23285,25 +23298,25 @@
         <v>80</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>78</v>
+        <v>534</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>78</v>
+        <v>535</v>
       </c>
     </row>
     <row r="175" hidden="true">
@@ -23311,7 +23324,7 @@
         <v>646</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23319,7 +23332,7 @@
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G175" t="s" s="2">
         <v>89</v>
@@ -23334,24 +23347,22 @@
         <v>78</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>223</v>
+        <v>104</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
-        <v>555</v>
+        <v>78</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>78</v>
@@ -23393,10 +23404,10 @@
         <v>78</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>227</v>
+        <v>106</v>
       </c>
       <c r="AG175" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH175" t="s" s="2">
         <v>89</v>
@@ -23414,7 +23425,7 @@
         <v>78</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>78</v>
@@ -23428,7 +23439,7 @@
         <v>647</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23436,10 +23447,10 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>78</v>
@@ -23451,13 +23462,13 @@
         <v>78</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>558</v>
+        <v>201</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23469,7 +23480,7 @@
         <v>78</v>
       </c>
       <c r="S176" t="s" s="2">
-        <v>638</v>
+        <v>78</v>
       </c>
       <c r="T176" t="s" s="2">
         <v>78</v>
@@ -23484,41 +23495,43 @@
         <v>78</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y176" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y176" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z176" t="s" s="2">
-        <v>559</v>
+        <v>78</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB176" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC176" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD176" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE176" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>233</v>
+        <v>117</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>78</v>
@@ -23527,7 +23540,7 @@
         <v>78</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>78</v>
@@ -23541,18 +23554,20 @@
         <v>648</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="C177" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="C177" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="D177" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>78</v>
@@ -23561,23 +23576,19 @@
         <v>78</v>
       </c>
       <c r="J177" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>153</v>
+        <v>546</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>395</v>
+        <v>547</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N177" s="2"/>
+      <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>78</v>
       </c>
@@ -23625,7 +23636,7 @@
         <v>78</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>399</v>
+        <v>117</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23637,16 +23648,16 @@
         <v>207</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>401</v>
+        <v>78</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>78</v>
@@ -23660,7 +23671,7 @@
         <v>649</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>578</v>
+        <v>550</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23680,23 +23691,19 @@
         <v>78</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K178" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>452</v>
+        <v>104</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N178" s="2"/>
+      <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>78</v>
       </c>
@@ -23744,7 +23751,7 @@
         <v>78</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>456</v>
+        <v>106</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23753,19 +23760,19 @@
         <v>89</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>457</v>
+        <v>78</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>458</v>
+        <v>107</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>78</v>
@@ -23779,11 +23786,9 @@
         <v>650</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C179" t="s" s="2">
-        <v>651</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
         <v>78</v>
       </c>
@@ -23792,7 +23797,7 @@
         <v>79</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H179" t="s" s="2">
         <v>78</v>
@@ -23801,23 +23806,19 @@
         <v>78</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>331</v>
+        <v>110</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>652</v>
+        <v>200</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N179" s="2"/>
+      <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
         <v>78</v>
       </c>
@@ -23841,31 +23842,31 @@
         <v>78</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>530</v>
+        <v>78</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>531</v>
+        <v>78</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC179" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD179" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE179" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>525</v>
+        <v>117</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -23874,33 +23875,33 @@
         <v>80</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>533</v>
+        <v>78</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23908,7 +23909,7 @@
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G180" t="s" s="2">
         <v>89</v>
@@ -23923,22 +23924,24 @@
         <v>78</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>104</v>
+        <v>223</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N180" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q180" s="2"/>
       <c r="R180" t="s" s="2">
-        <v>78</v>
+        <v>555</v>
       </c>
       <c r="S180" t="s" s="2">
         <v>78</v>
@@ -23980,10 +23983,10 @@
         <v>78</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>106</v>
+        <v>227</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>89</v>
@@ -24001,7 +24004,7 @@
         <v>78</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>78</v>
@@ -24012,10 +24015,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24023,10 +24026,10 @@
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>78</v>
@@ -24038,13 +24041,13 @@
         <v>78</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>201</v>
+        <v>558</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -24056,7 +24059,7 @@
         <v>78</v>
       </c>
       <c r="S181" t="s" s="2">
-        <v>78</v>
+        <v>643</v>
       </c>
       <c r="T181" t="s" s="2">
         <v>78</v>
@@ -24071,43 +24074,41 @@
         <v>78</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y181" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y181" s="2"/>
       <c r="Z181" t="s" s="2">
-        <v>78</v>
+        <v>559</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB181" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE181" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>117</v>
+        <v>233</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK181" t="s" s="2">
         <v>78</v>
@@ -24116,7 +24117,7 @@
         <v>78</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AN181" t="s" s="2">
         <v>78</v>
@@ -24127,23 +24128,21 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C182" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H182" t="s" s="2">
         <v>78</v>
@@ -24152,19 +24151,23 @@
         <v>78</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>546</v>
+        <v>153</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>547</v>
+        <v>395</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N182" s="2"/>
-      <c r="O182" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P182" t="s" s="2">
         <v>78</v>
       </c>
@@ -24212,7 +24215,7 @@
         <v>78</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>117</v>
+        <v>399</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
@@ -24224,16 +24227,16 @@
         <v>207</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>78</v>
@@ -24244,10 +24247,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24267,19 +24270,23 @@
         <v>78</v>
       </c>
       <c r="J183" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K183" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>104</v>
+        <v>452</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N183" s="2"/>
-      <c r="O183" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O183" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P183" t="s" s="2">
         <v>78</v>
       </c>
@@ -24327,7 +24334,7 @@
         <v>78</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>106</v>
+        <v>456</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -24336,19 +24343,19 @@
         <v>89</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>107</v>
+        <v>458</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>78</v>
@@ -24359,12 +24366,14 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C184" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="C184" t="s" s="2">
+        <v>656</v>
+      </c>
       <c r="D184" t="s" s="2">
         <v>78</v>
       </c>
@@ -24373,7 +24382,7 @@
         <v>79</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>78</v>
@@ -24382,19 +24391,23 @@
         <v>78</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>110</v>
+        <v>331</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>200</v>
+        <v>657</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N184" s="2"/>
-      <c r="O184" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N184" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O184" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P184" t="s" s="2">
         <v>78</v>
       </c>
@@ -24418,31 +24431,31 @@
         <v>78</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>78</v>
+        <v>530</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>78</v>
+        <v>531</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB184" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC184" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD184" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE184" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>117</v>
+        <v>525</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
@@ -24451,25 +24464,25 @@
         <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ184" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK184" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>78</v>
+        <v>534</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>78</v>
+        <v>535</v>
       </c>
     </row>
     <row r="185" hidden="true">
@@ -24477,7 +24490,7 @@
         <v>658</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24485,7 +24498,7 @@
       </c>
       <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G185" t="s" s="2">
         <v>89</v>
@@ -24500,24 +24513,22 @@
         <v>78</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>223</v>
+        <v>104</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N185" s="2"/>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>555</v>
+        <v>78</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>78</v>
@@ -24559,10 +24570,10 @@
         <v>78</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>227</v>
+        <v>106</v>
       </c>
       <c r="AG185" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH185" t="s" s="2">
         <v>89</v>
@@ -24580,7 +24591,7 @@
         <v>78</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="AN185" t="s" s="2">
         <v>78</v>
@@ -24594,7 +24605,7 @@
         <v>659</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24602,10 +24613,10 @@
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G186" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H186" t="s" s="2">
         <v>78</v>
@@ -24617,13 +24628,13 @@
         <v>78</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>558</v>
+        <v>201</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -24635,7 +24646,7 @@
         <v>78</v>
       </c>
       <c r="S186" t="s" s="2">
-        <v>651</v>
+        <v>78</v>
       </c>
       <c r="T186" t="s" s="2">
         <v>78</v>
@@ -24650,41 +24661,43 @@
         <v>78</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y186" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y186" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z186" t="s" s="2">
-        <v>559</v>
+        <v>78</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB186" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC186" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD186" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE186" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>233</v>
+        <v>117</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH186" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI186" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AJ186" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK186" t="s" s="2">
         <v>78</v>
@@ -24693,7 +24706,7 @@
         <v>78</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AN186" t="s" s="2">
         <v>78</v>
@@ -24707,18 +24720,20 @@
         <v>660</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="C187" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="C187" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="D187" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G187" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H187" t="s" s="2">
         <v>78</v>
@@ -24727,23 +24742,19 @@
         <v>78</v>
       </c>
       <c r="J187" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>153</v>
+        <v>546</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>395</v>
+        <v>547</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N187" s="2"/>
+      <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
         <v>78</v>
       </c>
@@ -24791,7 +24802,7 @@
         <v>78</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>399</v>
+        <v>117</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -24803,16 +24814,16 @@
         <v>207</v>
       </c>
       <c r="AJ187" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK187" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>401</v>
+        <v>78</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>78</v>
@@ -24826,7 +24837,7 @@
         <v>661</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>578</v>
+        <v>550</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24840,29 +24851,25 @@
         <v>89</v>
       </c>
       <c r="H188" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I188" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J188" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K188" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>452</v>
+        <v>104</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N188" s="2"/>
+      <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
         <v>78</v>
       </c>
@@ -24910,7 +24917,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>456</v>
+        <v>106</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -24919,19 +24926,19 @@
         <v>89</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK188" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>457</v>
+        <v>78</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>458</v>
+        <v>107</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>78</v>
@@ -24945,7 +24952,7 @@
         <v>662</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>662</v>
+        <v>552</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24956,32 +24963,28 @@
         <v>79</v>
       </c>
       <c r="G189" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H189" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I189" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J189" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>663</v>
+        <v>200</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="O189" t="s" s="2">
-        <v>666</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N189" s="2"/>
+      <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
         <v>78</v>
       </c>
@@ -25017,43 +25020,43 @@
         <v>78</v>
       </c>
       <c r="AB189" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC189" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD189" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE189" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>662</v>
+        <v>117</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH189" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>304</v>
+        <v>207</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>667</v>
+        <v>78</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>668</v>
+        <v>78</v>
       </c>
       <c r="AM189" t="s" s="2">
-        <v>669</v>
+        <v>78</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>670</v>
+        <v>78</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>78</v>
@@ -25061,10 +25064,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>671</v>
+        <v>554</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25072,13 +25075,13 @@
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H190" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I190" t="s" s="2">
         <v>78</v>
@@ -25087,26 +25090,24 @@
         <v>78</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>672</v>
+        <v>223</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>673</v>
+        <v>224</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="O190" t="s" s="2">
-        <v>675</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q190" s="2"/>
       <c r="R190" t="s" s="2">
-        <v>78</v>
+        <v>555</v>
       </c>
       <c r="S190" t="s" s="2">
         <v>78</v>
@@ -25148,28 +25149,28 @@
         <v>78</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>671</v>
+        <v>227</v>
       </c>
       <c r="AG190" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI190" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK190" t="s" s="2">
-        <v>676</v>
+        <v>78</v>
       </c>
       <c r="AL190" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM190" t="s" s="2">
-        <v>669</v>
+        <v>198</v>
       </c>
       <c r="AN190" t="s" s="2">
         <v>78</v>
@@ -25180,10 +25181,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>677</v>
+        <v>557</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25194,10 +25195,10 @@
         <v>79</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H191" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I191" t="s" s="2">
         <v>78</v>
@@ -25206,20 +25207,16 @@
         <v>78</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>678</v>
+        <v>175</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>679</v>
+        <v>231</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>682</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="N191" s="2"/>
+      <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
         <v>78</v>
       </c>
@@ -25228,7 +25225,7 @@
         <v>78</v>
       </c>
       <c r="S191" t="s" s="2">
-        <v>78</v>
+        <v>656</v>
       </c>
       <c r="T191" t="s" s="2">
         <v>78</v>
@@ -25243,53 +25240,53 @@
         <v>78</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>78</v>
+        <v>559</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB191" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="AC191" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC191" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD191" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE191" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>677</v>
+        <v>233</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI191" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>684</v>
+        <v>101</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>685</v>
+        <v>78</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>686</v>
+        <v>78</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>687</v>
+        <v>198</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>688</v>
+        <v>78</v>
       </c>
       <c r="AO191" t="s" s="2">
         <v>78</v>
@@ -25297,10 +25294,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>689</v>
+        <v>665</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>689</v>
+        <v>561</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25311,7 +25308,7 @@
         <v>79</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>78</v>
@@ -25320,19 +25317,23 @@
         <v>78</v>
       </c>
       <c r="J192" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>104</v>
+        <v>395</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N192" s="2"/>
-      <c r="O192" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N192" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O192" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P192" t="s" s="2">
         <v>78</v>
       </c>
@@ -25380,28 +25381,28 @@
         <v>78</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>106</v>
+        <v>399</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK192" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>107</v>
+        <v>401</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>78</v>
@@ -25412,44 +25413,46 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>690</v>
+        <v>666</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>690</v>
+        <v>578</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H193" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J193" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>111</v>
+        <v>452</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O193" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="O193" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P193" t="s" s="2">
         <v>78</v>
       </c>
@@ -25485,40 +25488,40 @@
         <v>78</v>
       </c>
       <c r="AB193" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC193" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE193" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>117</v>
+        <v>456</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI193" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AM193" t="s" s="2">
-        <v>107</v>
+        <v>458</v>
       </c>
       <c r="AN193" t="s" s="2">
         <v>78</v>
@@ -25529,14 +25532,12 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>691</v>
+        <v>667</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="C194" t="s" s="2">
-        <v>692</v>
-      </c>
+        <v>667</v>
+      </c>
+      <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
         <v>78</v>
       </c>
@@ -25548,25 +25549,29 @@
         <v>89</v>
       </c>
       <c r="H194" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I194" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J194" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>693</v>
+        <v>103</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>694</v>
+        <v>668</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="N194" s="2"/>
-      <c r="O194" s="2"/>
+        <v>669</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>671</v>
+      </c>
       <c r="P194" t="s" s="2">
         <v>78</v>
       </c>
@@ -25614,31 +25619,31 @@
         <v>78</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>117</v>
+        <v>667</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI194" t="s" s="2">
-        <v>78</v>
+        <v>304</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>78</v>
+        <v>672</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>78</v>
+        <v>673</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>78</v>
+        <v>674</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>78</v>
+        <v>675</v>
       </c>
       <c r="AO194" t="s" s="2">
         <v>78</v>
@@ -25646,10 +25651,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>696</v>
+        <v>676</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>696</v>
+        <v>676</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -25657,31 +25662,35 @@
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H195" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I195" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J195" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>175</v>
+        <v>103</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>697</v>
+        <v>677</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="N195" s="2"/>
-      <c r="O195" s="2"/>
+        <v>678</v>
+      </c>
+      <c r="N195" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="O195" t="s" s="2">
+        <v>680</v>
+      </c>
       <c r="P195" t="s" s="2">
         <v>78</v>
       </c>
@@ -25705,13 +25714,13 @@
         <v>78</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>324</v>
+        <v>78</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>699</v>
+        <v>78</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>700</v>
+        <v>78</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>78</v>
@@ -25729,31 +25738,31 @@
         <v>78</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>701</v>
+        <v>676</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI195" t="s" s="2">
-        <v>702</v>
+        <v>78</v>
       </c>
       <c r="AJ195" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>78</v>
+        <v>681</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>703</v>
+        <v>78</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>704</v>
+        <v>674</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>705</v>
+        <v>78</v>
       </c>
       <c r="AO195" t="s" s="2">
         <v>78</v>
@@ -25761,10 +25770,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>706</v>
+        <v>682</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>706</v>
+        <v>682</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -25772,34 +25781,34 @@
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H196" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I196" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J196" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>103</v>
+        <v>683</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>707</v>
+        <v>684</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>708</v>
+        <v>685</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>709</v>
+        <v>686</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>710</v>
+        <v>687</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>78</v>
@@ -25836,43 +25845,41 @@
         <v>78</v>
       </c>
       <c r="AB196" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC196" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>688</v>
+      </c>
+      <c r="AC196" s="2"/>
       <c r="AD196" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE196" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>711</v>
+        <v>682</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>101</v>
+        <v>689</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>78</v>
+        <v>690</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>712</v>
+        <v>691</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>713</v>
+        <v>692</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>362</v>
+        <v>693</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>78</v>
@@ -25880,10 +25887,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>714</v>
+        <v>694</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>714</v>
+        <v>694</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25900,26 +25907,22 @@
         <v>78</v>
       </c>
       <c r="I197" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J197" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>175</v>
+        <v>103</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>715</v>
+        <v>104</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="O197" t="s" s="2">
-        <v>718</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N197" s="2"/>
+      <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
         <v>78</v>
       </c>
@@ -25943,13 +25946,13 @@
         <v>78</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>324</v>
+        <v>78</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>719</v>
+        <v>78</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>720</v>
+        <v>78</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>78</v>
@@ -25967,7 +25970,7 @@
         <v>78</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>721</v>
+        <v>106</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>79</v>
@@ -25979,19 +25982,19 @@
         <v>78</v>
       </c>
       <c r="AJ197" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK197" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>722</v>
+        <v>78</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>723</v>
+        <v>107</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>724</v>
+        <v>78</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>78</v>
@@ -25999,21 +26002,21 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>725</v>
+        <v>695</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>725</v>
+        <v>695</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G198" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H198" t="s" s="2">
         <v>78</v>
@@ -26022,19 +26025,19 @@
         <v>78</v>
       </c>
       <c r="J198" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>726</v>
+        <v>110</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>727</v>
+        <v>111</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>728</v>
+        <v>112</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>729</v>
+        <v>113</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -26072,37 +26075,37 @@
         <v>78</v>
       </c>
       <c r="AB198" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC198" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD198" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE198" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>730</v>
+        <v>117</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH198" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI198" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ198" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK198" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="AM198" t="s" s="2">
         <v>107</v>
@@ -26116,12 +26119,14 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>731</v>
+        <v>696</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C199" s="2"/>
+        <v>695</v>
+      </c>
+      <c r="C199" t="s" s="2">
+        <v>697</v>
+      </c>
       <c r="D199" t="s" s="2">
         <v>78</v>
       </c>
@@ -26139,16 +26144,16 @@
         <v>78</v>
       </c>
       <c r="J199" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>230</v>
+        <v>698</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>732</v>
+        <v>699</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>733</v>
+        <v>700</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -26199,31 +26204,31 @@
         <v>78</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>734</v>
+        <v>117</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH199" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI199" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ199" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK199" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL199" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AM199" t="s" s="2">
-        <v>735</v>
+        <v>78</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>370</v>
+        <v>78</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>78</v>
@@ -26231,23 +26236,21 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>736</v>
+        <v>701</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="C200" t="s" s="2">
-        <v>737</v>
-      </c>
+        <v>701</v>
+      </c>
+      <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G200" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H200" t="s" s="2">
         <v>78</v>
@@ -26256,23 +26259,19 @@
         <v>78</v>
       </c>
       <c r="J200" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>738</v>
+        <v>175</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>739</v>
+        <v>702</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="O200" t="s" s="2">
-        <v>682</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="N200" s="2"/>
+      <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
         <v>78</v>
       </c>
@@ -26296,13 +26295,13 @@
         <v>78</v>
       </c>
       <c r="X200" t="s" s="2">
-        <v>78</v>
+        <v>324</v>
       </c>
       <c r="Y200" t="s" s="2">
-        <v>78</v>
+        <v>704</v>
       </c>
       <c r="Z200" t="s" s="2">
-        <v>78</v>
+        <v>705</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>78</v>
@@ -26320,31 +26319,31 @@
         <v>78</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>677</v>
+        <v>706</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH200" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>207</v>
+        <v>707</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>684</v>
+        <v>101</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>740</v>
+        <v>78</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>686</v>
+        <v>708</v>
       </c>
       <c r="AM200" t="s" s="2">
-        <v>687</v>
+        <v>709</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>688</v>
+        <v>710</v>
       </c>
       <c r="AO200" t="s" s="2">
         <v>78</v>
@@ -26352,10 +26351,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>741</v>
+        <v>711</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>741</v>
+        <v>711</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26363,34 +26362,34 @@
       </c>
       <c r="E201" s="2"/>
       <c r="F201" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G201" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H201" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I201" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J201" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I201" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J201" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K201" t="s" s="2">
-        <v>742</v>
+        <v>103</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>743</v>
+        <v>712</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>744</v>
+        <v>713</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>745</v>
+        <v>714</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>746</v>
+        <v>715</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>78</v>
@@ -26439,31 +26438,31 @@
         <v>78</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>741</v>
+        <v>716</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH201" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>747</v>
+        <v>101</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>748</v>
+        <v>78</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>749</v>
+        <v>717</v>
       </c>
       <c r="AM201" t="s" s="2">
-        <v>750</v>
+        <v>718</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>751</v>
+        <v>362</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>78</v>
@@ -26471,10 +26470,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>752</v>
+        <v>719</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>752</v>
+        <v>719</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26491,23 +26490,25 @@
         <v>78</v>
       </c>
       <c r="I202" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J202" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>753</v>
+        <v>175</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>754</v>
+        <v>720</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="N202" s="2"/>
+        <v>721</v>
+      </c>
+      <c r="N202" t="s" s="2">
+        <v>722</v>
+      </c>
       <c r="O202" t="s" s="2">
-        <v>756</v>
+        <v>723</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>78</v>
@@ -26532,13 +26533,13 @@
         <v>78</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>78</v>
+        <v>324</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>78</v>
+        <v>724</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>78</v>
+        <v>725</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>78</v>
@@ -26556,7 +26557,7 @@
         <v>78</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>752</v>
+        <v>726</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>79</v>
@@ -26574,13 +26575,13 @@
         <v>78</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>521</v>
+        <v>727</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>757</v>
+        <v>728</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>107</v>
+        <v>729</v>
       </c>
       <c r="AO202" t="s" s="2">
         <v>78</v>
@@ -26588,10 +26589,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>758</v>
+        <v>730</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>758</v>
+        <v>730</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -26611,18 +26612,20 @@
         <v>78</v>
       </c>
       <c r="J203" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>103</v>
+        <v>731</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>104</v>
+        <v>732</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N203" s="2"/>
+        <v>733</v>
+      </c>
+      <c r="N203" t="s" s="2">
+        <v>734</v>
+      </c>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
         <v>78</v>
@@ -26671,7 +26674,7 @@
         <v>78</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>106</v>
+        <v>735</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>79</v>
@@ -26683,13 +26686,13 @@
         <v>78</v>
       </c>
       <c r="AJ203" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK203" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL203" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="AM203" t="s" s="2">
         <v>107</v>
@@ -26703,21 +26706,21 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>759</v>
+        <v>736</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>759</v>
+        <v>736</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G204" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H204" t="s" s="2">
         <v>78</v>
@@ -26726,20 +26729,18 @@
         <v>78</v>
       </c>
       <c r="J204" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>111</v>
+        <v>737</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N204" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>738</v>
+      </c>
+      <c r="N204" s="2"/>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
         <v>78</v>
@@ -26776,43 +26777,43 @@
         <v>78</v>
       </c>
       <c r="AB204" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC204" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD204" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE204" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>117</v>
+        <v>739</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH204" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI204" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK204" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>107</v>
+        <v>740</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>78</v>
+        <v>370</v>
       </c>
       <c r="AO204" t="s" s="2">
         <v>78</v>
@@ -26820,12 +26821,14 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>760</v>
+        <v>741</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="C205" s="2"/>
+        <v>682</v>
+      </c>
+      <c r="C205" t="s" s="2">
+        <v>742</v>
+      </c>
       <c r="D205" t="s" s="2">
         <v>78</v>
       </c>
@@ -26834,7 +26837,7 @@
         <v>79</v>
       </c>
       <c r="G205" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H205" t="s" s="2">
         <v>78</v>
@@ -26843,21 +26846,23 @@
         <v>78</v>
       </c>
       <c r="J205" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>103</v>
+        <v>743</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>761</v>
+        <v>744</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>762</v>
+        <v>685</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="O205" s="2"/>
+        <v>686</v>
+      </c>
+      <c r="O205" t="s" s="2">
+        <v>687</v>
+      </c>
       <c r="P205" t="s" s="2">
         <v>78</v>
       </c>
@@ -26905,31 +26910,31 @@
         <v>78</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>764</v>
+        <v>682</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH205" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI205" t="s" s="2">
-        <v>765</v>
+        <v>207</v>
       </c>
       <c r="AJ205" t="s" s="2">
-        <v>101</v>
+        <v>689</v>
       </c>
       <c r="AK205" t="s" s="2">
-        <v>78</v>
+        <v>745</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>78</v>
+        <v>691</v>
       </c>
       <c r="AM205" t="s" s="2">
-        <v>198</v>
+        <v>692</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>78</v>
+        <v>693</v>
       </c>
       <c r="AO205" t="s" s="2">
         <v>78</v>
@@ -26937,10 +26942,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>766</v>
+        <v>746</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>766</v>
+        <v>746</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -26951,30 +26956,32 @@
         <v>79</v>
       </c>
       <c r="G206" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H206" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I206" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J206" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>136</v>
+        <v>747</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>767</v>
+        <v>748</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>768</v>
+        <v>749</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>769</v>
-      </c>
-      <c r="O206" s="2"/>
+        <v>750</v>
+      </c>
+      <c r="O206" t="s" s="2">
+        <v>751</v>
+      </c>
       <c r="P206" t="s" s="2">
         <v>78</v>
       </c>
@@ -26998,11 +27005,13 @@
         <v>78</v>
       </c>
       <c r="X206" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y206" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y206" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z206" t="s" s="2">
-        <v>539</v>
+        <v>78</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>78</v>
@@ -27020,31 +27029,31 @@
         <v>78</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>770</v>
+        <v>746</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH206" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI206" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>101</v>
+        <v>752</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>78</v>
+        <v>753</v>
       </c>
       <c r="AL206" t="s" s="2">
-        <v>78</v>
+        <v>754</v>
       </c>
       <c r="AM206" t="s" s="2">
-        <v>198</v>
+        <v>755</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>78</v>
+        <v>756</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>78</v>
@@ -27052,10 +27061,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27078,18 +27087,18 @@
         <v>90</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>298</v>
+        <v>758</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="O207" s="2"/>
+        <v>760</v>
+      </c>
+      <c r="N207" s="2"/>
+      <c r="O207" t="s" s="2">
+        <v>761</v>
+      </c>
       <c r="P207" t="s" s="2">
         <v>78</v>
       </c>
@@ -27137,7 +27146,7 @@
         <v>78</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>775</v>
+        <v>757</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>79</v>
@@ -27155,13 +27164,13 @@
         <v>78</v>
       </c>
       <c r="AL207" t="s" s="2">
-        <v>78</v>
+        <v>521</v>
       </c>
       <c r="AM207" t="s" s="2">
-        <v>776</v>
+        <v>762</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="AO207" t="s" s="2">
         <v>78</v>
@@ -27169,10 +27178,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27192,20 +27201,18 @@
         <v>78</v>
       </c>
       <c r="J208" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K208" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>778</v>
+        <v>104</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>780</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N208" s="2"/>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>78</v>
@@ -27254,7 +27261,7 @@
         <v>78</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>781</v>
+        <v>106</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>79</v>
@@ -27266,7 +27273,7 @@
         <v>78</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK208" t="s" s="2">
         <v>78</v>
@@ -27275,7 +27282,7 @@
         <v>78</v>
       </c>
       <c r="AM208" t="s" s="2">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="AN208" t="s" s="2">
         <v>78</v>
@@ -27286,14 +27293,14 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>782</v>
+        <v>764</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>782</v>
+        <v>764</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
@@ -27312,20 +27319,18 @@
         <v>78</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>783</v>
+        <v>110</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>784</v>
+        <v>111</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>785</v>
+        <v>112</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="O209" t="s" s="2">
-        <v>787</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
         <v>78</v>
       </c>
@@ -27361,19 +27366,19 @@
         <v>78</v>
       </c>
       <c r="AB209" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC209" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD209" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE209" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>782</v>
+        <v>117</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>79</v>
@@ -27385,7 +27390,7 @@
         <v>78</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK209" t="s" s="2">
         <v>78</v>
@@ -27394,7 +27399,7 @@
         <v>78</v>
       </c>
       <c r="AM209" t="s" s="2">
-        <v>788</v>
+        <v>107</v>
       </c>
       <c r="AN209" t="s" s="2">
         <v>78</v>
@@ -27405,10 +27410,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>789</v>
+        <v>765</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>789</v>
+        <v>765</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27428,18 +27433,20 @@
         <v>78</v>
       </c>
       <c r="J210" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K210" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>104</v>
+        <v>766</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N210" s="2"/>
+        <v>767</v>
+      </c>
+      <c r="N210" t="s" s="2">
+        <v>768</v>
+      </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
         <v>78</v>
@@ -27488,7 +27495,7 @@
         <v>78</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>106</v>
+        <v>769</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>79</v>
@@ -27497,10 +27504,10 @@
         <v>89</v>
       </c>
       <c r="AI210" t="s" s="2">
-        <v>78</v>
+        <v>770</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK210" t="s" s="2">
         <v>78</v>
@@ -27509,7 +27516,7 @@
         <v>78</v>
       </c>
       <c r="AM210" t="s" s="2">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="AN210" t="s" s="2">
         <v>78</v>
@@ -27520,21 +27527,21 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>78</v>
@@ -27543,19 +27550,19 @@
         <v>78</v>
       </c>
       <c r="J211" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>111</v>
+        <v>772</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>112</v>
+        <v>773</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>113</v>
+        <v>774</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
@@ -27581,13 +27588,11 @@
         <v>78</v>
       </c>
       <c r="X211" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y211" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y211" s="2"/>
       <c r="Z211" t="s" s="2">
-        <v>78</v>
+        <v>539</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>78</v>
@@ -27605,19 +27610,19 @@
         <v>78</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>117</v>
+        <v>775</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI211" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK211" t="s" s="2">
         <v>78</v>
@@ -27626,7 +27631,7 @@
         <v>78</v>
       </c>
       <c r="AM211" t="s" s="2">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="AN211" t="s" s="2">
         <v>78</v>
@@ -27637,46 +27642,44 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>791</v>
+        <v>776</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>791</v>
+        <v>776</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>792</v>
+        <v>78</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H212" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I212" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J212" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>110</v>
+        <v>298</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O212" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>779</v>
+      </c>
+      <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>78</v>
       </c>
@@ -27724,19 +27727,19 @@
         <v>78</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI212" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK212" t="s" s="2">
         <v>78</v>
@@ -27745,7 +27748,7 @@
         <v>78</v>
       </c>
       <c r="AM212" t="s" s="2">
-        <v>198</v>
+        <v>781</v>
       </c>
       <c r="AN212" t="s" s="2">
         <v>78</v>
@@ -27756,10 +27759,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>796</v>
+        <v>782</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>796</v>
+        <v>782</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -27779,21 +27782,21 @@
         <v>78</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>331</v>
+        <v>103</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>797</v>
+        <v>783</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="N213" s="2"/>
-      <c r="O213" t="s" s="2">
-        <v>799</v>
-      </c>
+        <v>784</v>
+      </c>
+      <c r="N213" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
         <v>78</v>
       </c>
@@ -27817,13 +27820,13 @@
         <v>78</v>
       </c>
       <c r="X213" t="s" s="2">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>800</v>
+        <v>78</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>801</v>
+        <v>78</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>78</v>
@@ -27841,7 +27844,7 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>79</v>
@@ -27862,7 +27865,7 @@
         <v>78</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>802</v>
+        <v>198</v>
       </c>
       <c r="AN213" t="s" s="2">
         <v>78</v>
@@ -27873,10 +27876,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>803</v>
+        <v>787</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>803</v>
+        <v>787</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -27887,7 +27890,7 @@
         <v>79</v>
       </c>
       <c r="G214" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H214" t="s" s="2">
         <v>78</v>
@@ -27899,17 +27902,19 @@
         <v>78</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="N214" s="2"/>
+        <v>790</v>
+      </c>
+      <c r="N214" t="s" s="2">
+        <v>791</v>
+      </c>
       <c r="O214" t="s" s="2">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -27958,13 +27963,13 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>803</v>
+        <v>787</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH214" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI214" t="s" s="2">
         <v>78</v>
@@ -27976,10 +27981,10 @@
         <v>78</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>808</v>
+        <v>78</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>809</v>
+        <v>793</v>
       </c>
       <c r="AN214" t="s" s="2">
         <v>78</v>
@@ -27990,10 +27995,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>810</v>
+        <v>794</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>810</v>
+        <v>794</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28004,7 +28009,7 @@
         <v>79</v>
       </c>
       <c r="G215" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H215" t="s" s="2">
         <v>78</v>
@@ -28016,18 +28021,16 @@
         <v>78</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>678</v>
+        <v>103</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>811</v>
+        <v>104</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>680</v>
+        <v>105</v>
       </c>
       <c r="N215" s="2"/>
-      <c r="O215" t="s" s="2">
-        <v>812</v>
-      </c>
+      <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>78</v>
       </c>
@@ -28075,31 +28078,31 @@
         <v>78</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>810</v>
+        <v>106</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH215" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI215" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>813</v>
+        <v>78</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL215" t="s" s="2">
-        <v>686</v>
+        <v>78</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>687</v>
+        <v>107</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>688</v>
+        <v>78</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>78</v>
@@ -28107,21 +28110,21 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>814</v>
+        <v>795</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>814</v>
+        <v>795</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>78</v>
@@ -28133,20 +28136,18 @@
         <v>78</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>815</v>
+        <v>110</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>816</v>
+        <v>111</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>744</v>
+        <v>112</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="O216" t="s" s="2">
-        <v>817</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
         <v>78</v>
       </c>
@@ -28194,31 +28195,31 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>814</v>
+        <v>117</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH216" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK216" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>749</v>
+        <v>78</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>750</v>
+        <v>107</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>751</v>
+        <v>78</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>78</v>
@@ -28226,14 +28227,14 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
-        <v>78</v>
+        <v>797</v>
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
@@ -28243,26 +28244,28 @@
         <v>80</v>
       </c>
       <c r="H217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I217" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I217" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J217" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>819</v>
+        <v>110</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>820</v>
+        <v>798</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="N217" s="2"/>
+        <v>799</v>
+      </c>
+      <c r="N217" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O217" t="s" s="2">
-        <v>822</v>
+        <v>295</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>78</v>
@@ -28311,7 +28314,7 @@
         <v>78</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>818</v>
+        <v>800</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>79</v>
@@ -28323,26 +28326,613 @@
         <v>78</v>
       </c>
       <c r="AJ217" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM217" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AN217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO217" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="218" hidden="true">
+      <c r="A218" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="C218" s="2"/>
+      <c r="D218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E218" s="2"/>
+      <c r="F218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G218" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K218" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L218" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="M218" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="N218" s="2"/>
+      <c r="O218" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="P218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q218" s="2"/>
+      <c r="R218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X218" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y218" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="Z218" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="AA218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF218" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="AG218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH218" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ218" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK217" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL217" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM217" t="s" s="2">
+      <c r="AK218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM218" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="AN218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO218" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="219" hidden="true">
+      <c r="A219" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="C219" s="2"/>
+      <c r="D219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E219" s="2"/>
+      <c r="F219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G219" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K219" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="L219" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="M219" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="N219" s="2"/>
+      <c r="O219" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="P219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q219" s="2"/>
+      <c r="R219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF219" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="AG219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH219" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ219" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL219" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="AM219" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="AN219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO219" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="220" hidden="true">
+      <c r="A220" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="B220" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="C220" s="2"/>
+      <c r="D220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E220" s="2"/>
+      <c r="F220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G220" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K220" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="L220" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="M220" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="N220" s="2"/>
+      <c r="O220" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="P220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q220" s="2"/>
+      <c r="R220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF220" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="AG220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH220" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI220" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AJ220" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="AK220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL220" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="AM220" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="AN220" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AO220" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="221" hidden="true">
+      <c r="A221" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="C221" s="2"/>
+      <c r="D221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E221" s="2"/>
+      <c r="F221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G221" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K221" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="L221" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="M221" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="N221" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="O221" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="P221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q221" s="2"/>
+      <c r="R221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF221" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="AG221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH221" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI221" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AJ221" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL221" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="AM221" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="AN221" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="AO221" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="222" hidden="true">
+      <c r="A222" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="C222" s="2"/>
+      <c r="D222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E222" s="2"/>
+      <c r="F222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G222" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H222" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K222" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="L222" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="M222" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="N222" s="2"/>
+      <c r="O222" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="P222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q222" s="2"/>
+      <c r="R222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF222" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="AG222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH222" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ222" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM222" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="AN217" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO217" t="s" s="2">
+      <c r="AN222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO222" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO217">
+  <autoFilter ref="A1:AO222">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -28352,7 +28942,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI216">
+  <conditionalFormatting sqref="A2:AI221">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:09:44+00:00</t>
+    <t>2025-02-11T15:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T15:24:25+00:00</t>
+    <t>2025-03-18T14:02:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -397,7 +397,7 @@
     <t>as-ext-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -934,7 +934,7 @@
     <t>as-ext-digital-certificate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -950,7 +950,7 @@
     <t>as-ext-organization-pharmacy-licence</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pharmacy-licence|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pharmacy-licence|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -966,7 +966,7 @@
     <t>as-ext-organization-pricing-model</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pricing-model|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pricing-model|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -982,7 +982,7 @@
     <t>as-ext-organization-closing-type</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-closing-type|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-closing-type|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -998,7 +998,7 @@
     <t>as-ext-organization-budget-type</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-budget-type|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-budget-type|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1014,7 +1014,7 @@
     <t>as-ext-organization-authorization-deadline</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-authorization-deadline|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-authorization-deadline|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1800,7 +1800,7 @@
     <t>as-ext-organization-types</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-types|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-types|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1840,7 +1840,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-organization-types|1.2.0-snapshot-2</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-organization-types|1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Organization.type:organizationType.coding</t>
@@ -2107,7 +2107,7 @@
     <t>Le type d’établissement détermine si c'est un établissement principal ou secondaire.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-type-etablissement|1.2.0-snapshot-2</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-type-etablissement|1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>EntiteGeographique.typeEtablissement</t>
@@ -2244,7 +2244,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-2}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2326,7 +2326,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2607,7 +2607,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-2}
+    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2649,7 +2649,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-3)
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/main/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
